--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -10,11 +10,13 @@
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Parts" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Ore" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Battery" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Outposts" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Pet" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Caves" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Parts" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Ore" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Dig times" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Battery" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Progress" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pet" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,9 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="130">
-  <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.5)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="194">
+  <si>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.7)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -46,25 +48,31 @@
     <t xml:space="preserve">Black text = a formula worked out from the settings</t>
   </si>
   <si>
-    <t xml:space="preserve">Green text = pulled from the Settings tab</t>
+    <t xml:space="preserve">Green text = pulled from another tab</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Settings – the shared numbers (dig rate, battery costs, conveyor, relic, ore depth bonus)</t>
+    <t xml:space="preserve">Settings – shared numbers (dig rate, battery, conveyor, bridges, caches, depth bonus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caves – the three caves: ore and hard-rock chances, value multiplier, relic, outpost, bridge and cache payouts</t>
   </si>
   <si>
     <t xml:space="preserve">Parts – every part, its cost and stats, and the total cost to max each slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Ore – what each ore sells for at each outpost depth, and how long it takes to dig with each arm tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battery – how far each body can go on one charge with each set of legs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outposts – conveyor cost and depth for each outpost</t>
+    <t xml:space="preserve">Ore – what each ore sells for at the start, outpost and end of each cave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dig times – seconds to break each block with each arm tier ("—" = too hard for that tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery – how far each tank can go on one charge with each set of legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress – a rough cost path through the three caves</t>
   </si>
   <si>
     <t xml:space="preserve">Pet – Pip the Mole: earnings and training cost per level</t>
@@ -109,58 +117,184 @@
     <t xml:space="preserve">Ore is worth +100% for every this many blocks of depth (ORE_DEPTH_BONUS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Base rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rows in the base yard (BASE_ROWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost spacing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocks between outposts (CONVEYOR.step)</t>
+    <t xml:space="preserve">Outpost depth (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depth of each cave's outpost (CONVEYOR.step)</t>
   </si>
   <si>
     <t xml:space="preserve">Outpost base cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Cost of the first outpost (CONVEYOR.baseCost)</t>
+    <t xml:space="preserve">Outpost cost in cave 1 (CONVEYOR.baseCost)</t>
   </si>
   <si>
     <t xml:space="preserve">Outpost cost growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Each outpost costs this many times the last (CONVEYOR.costGrowth)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relic row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row of the Ancient Relic (RELIC.row)</t>
+    <t xml:space="preserve">Each cave's outpost costs this many times the last (CONVEYOR.costGrowth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache coins min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smallest cache coin payout before the cave multiplier (CACHE.coins[0])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache coins max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest cache coin payout before the cave multiplier (CACHE.coins[1])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache ore pieces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieces of the cave's best ore in each cache (CACHE.ores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caches per cave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many caches each cave hides (CACHE.perCave)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relic depth (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depth of each cave's relic chamber (RELIC.row 57 − 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recall keeps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of ore kept on a manual recall (RECALL.keepCargo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockfall shake time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How long unstable rock shakes before it falls (ROCK.wobble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockfall trigger radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walking this close to unstable rock with an open side sets it off (ROCK.triggerRadius)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave-in battery loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of max battery lost in a cave-in (ROCK.batteryLoss)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave-in cargo loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of ore lost in a cave-in (ROCK.cargoLoss)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore value ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore 1 chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore 2 chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsidian chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unstable rock chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chasms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relic</t>
   </si>
   <si>
     <t xml:space="preserve">Relic reward</t>
   </si>
   <si>
-    <t xml:space="preserve">Coins for bringing the relic back (RELIC.reward)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recall keeps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of ore kept on a manual recall (RECALL.keepCargo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cave-in battery loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of max battery lost in a cave-in (ROCK.batteryLoss)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cave-in cargo loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of ore lost in a cave-in (ROCK.cargoLoss)</t>
+    <t xml:space="preserve">Halfway outpost cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge keys (= pads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache coins (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache coins (max)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relic needs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Topsoil Hollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ember Idol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rock Claws (no seal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite Rift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storm Lens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drill Arms (granite seal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basalt Deeps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plasma Cutters (obsidian seal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard rock is rarer near the cave mouth: its chance scales from 40% of the listed value at the entrance to 140% at the relic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each bridge pad needs one of that cave's bridge keys; one marked key cache per pad is hidden before the chasm. Cave 2 also has an old bridge; cave 3 does not.</t>
   </si>
   <si>
     <t xml:space="preserve">Slot</t>
@@ -184,43 +318,55 @@
     <t xml:space="preserve">Cumulative cost in slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Head</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optic Bulb</t>
+    <t xml:space="preserve">Canopy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Bubble</t>
   </si>
   <si>
     <t xml:space="preserve">Light (blocks)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rock scan (blocks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scanner Dome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Eye</t>
+    <t xml:space="preserve">Scanner range (blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armored Visor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor Dome</t>
   </si>
   <si>
     <t xml:space="preserve">Arms</t>
   </si>
   <si>
-    <t xml:space="preserve">Pincers</t>
+    <t xml:space="preserve">Rock Claws</t>
   </si>
   <si>
     <t xml:space="preserve">Dig power</t>
   </si>
   <si>
+    <t xml:space="preserve">Breaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft rock</t>
+  </si>
+  <si>
     <t xml:space="preserve">Drill Arms</t>
   </si>
   <si>
+    <t xml:space="preserve">+ granite</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plasma Cutters</t>
   </si>
   <si>
-    <t xml:space="preserve">Body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tin Can</t>
+    <t xml:space="preserve">+ obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Tank</t>
   </si>
   <si>
     <t xml:space="preserve">Battery</t>
@@ -229,16 +375,16 @@
     <t xml:space="preserve">Cargo (ore)</t>
   </si>
   <si>
-    <t xml:space="preserve">Iron Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactor</t>
+    <t xml:space="preserve">Twin Tanks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactor Tank</t>
   </si>
   <si>
     <t xml:space="preserve">Legs</t>
   </si>
   <si>
-    <t xml:space="preserve">Rusty Treads</t>
+    <t xml:space="preserve">Piston Legs</t>
   </si>
   <si>
     <t xml:space="preserve">Speed (blocks/s)</t>
@@ -247,7 +393,7 @@
     <t xml:space="preserve">Move cost share</t>
   </si>
   <si>
-    <t xml:space="preserve">Spring Legs</t>
+    <t xml:space="preserve">Spring Struts</t>
   </si>
   <si>
     <t xml:space="preserve">Hover Jets</t>
@@ -262,52 +408,46 @@
     <t xml:space="preserve">Base value</t>
   </si>
   <si>
+    <t xml:space="preserve">At the mouth (1 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the outpost (25 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the relic (54 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value = base value × cave multiplier × (1 + depth ÷ ore depth bonus). Caches pay in the cave's best (second) ore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block</t>
+  </si>
+  <si>
     <t xml:space="preserve">Toughness (hp)</t>
   </si>
   <si>
-    <t xml:space="preserve">Value at 0 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 25 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 50 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 75 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 100 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 125 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value at 150 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig s · Pincers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig s · Drills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig s · Plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain blocks</t>
+    <t xml:space="preserve">Needs arms tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rock Claws (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drill Arms (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plasma Cutters (s)</t>
   </si>
   <si>
     <t xml:space="preserve">Dirt</t>
@@ -316,6 +456,9 @@
     <t xml:space="preserve">Clay</t>
   </si>
   <si>
+    <t xml:space="preserve">Stone</t>
+  </si>
+  <si>
     <t xml:space="preserve">Basalt</t>
   </si>
   <si>
@@ -325,10 +468,16 @@
     <t xml:space="preserve">Rubble</t>
   </si>
   <si>
-    <t xml:space="preserve">Ancient Relic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig times ignore the pet bonus (+8% dig power per pet level).</t>
+    <t xml:space="preserve">Treasure cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignores the pet bonus (+8% dig power per pet level). Relics in caves 2 and 3 are sealed in granite / obsidian, so you need that tier to reach them.</t>
   </si>
   <si>
     <t xml:space="preserve">Blocks you can walk</t>
@@ -337,34 +486,82 @@
     <t xml:space="preserve">Blocks of new tunnel</t>
   </si>
   <si>
-    <t xml:space="preserve">Round trip depth (new tunnel out, walk back)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Straight-line estimates: no detours, no cave-ins, and walking back the way you came. Riding the conveyor costs nothing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depth (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocks of conveyor path to dig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk from last outpost to relic (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The conveyor stops at Outpost 5 so the last stretch to the relic is on foot.</t>
+    <t xml:space="preserve">Round trip depth (tunnel out, walk back)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-line estimates: no detours or cave-ins, walking back the way you came. Riding the conveyor is free. Compare with the outpost at 25 m and the relic at 54 m.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend (coins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earn (coins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 1: Drill Arms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap, and needed for granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 1: halfway outpost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The entrance outpost is free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 1: Ember Idol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocks cave 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2: Armored Visor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scanner finds caches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2: Twin Tanks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room for the longer trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2: halfway outpost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2: Storm Lens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocks cave 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 3: Plasma Cutters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needed for the obsidian seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 3: halfway outpost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 3: Core Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End of v0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending only (ore income not counted). A negative running total is the ore you need to earn by digging before that step.</t>
   </si>
   <si>
     <t xml:space="preserve">Seconds per block at level 1</t>
@@ -382,7 +579,7 @@
     <t xml:space="preserve">Ore multiplier</t>
   </si>
   <si>
-    <t xml:space="preserve">Dig bonus to robot per level</t>
+    <t xml:space="preserve">Dig bonus to walker per level</t>
   </si>
   <si>
     <t xml:space="preserve">First training cost</t>
@@ -403,7 +600,7 @@
     <t xml:space="preserve">Coins per minute</t>
   </si>
   <si>
-    <t xml:space="preserve">Robot dig bonus</t>
+    <t xml:space="preserve">Walker dig bonus</t>
   </si>
   <si>
     <t xml:space="preserve">Cost to train to this level</t>
@@ -412,23 +609,23 @@
     <t xml:space="preserve">Cumulative training</t>
   </si>
   <si>
-    <t xml:space="preserve">Hatched from the fossil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Coins per minute" includes the bonus from ore blocks (ore chance × ore multiplier).</t>
+    <t xml:space="preserve">Hatched from the fossil (cave 1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
-    <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0\×"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -553,7 +750,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -594,15 +791,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,19 +819,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -882,7 +1091,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -962,6 +1171,16 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -980,177 +1199,221 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>60</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>80</v>
+        <v>2.5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1.6</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0.5</v>
+        <v>41</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0.25</v>
+        <v>43</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>54</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>44</v>
+      <c r="C19" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1169,404 +1432,277 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="9" t="n">
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="J2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="10" t="n">
-        <f aca="false">SUM(D2:D2)</f>
+      <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="O2" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A2-1),0)</f>
+        <v>80</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="R2" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$11*C2,0)</f>
+        <v>160</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="9" t="n">
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A3-1),0)</f>
+        <v>200</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C3,0)</f>
         <v>120</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="R3" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$11*C3,0)</f>
+        <v>320</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="10" t="n">
-        <f aca="false">SUM(D2:D3)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">SUM(D2:D4)</f>
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="10" t="n">
-        <f aca="false">SUM(D5:D5)</f>
-        <v>0</v>
+      <c r="M4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O4" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A4-1),0)</f>
+        <v>500</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C4,0)</f>
+        <v>210</v>
+      </c>
+      <c r="R4" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$11*C4,0)</f>
+        <v>560</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="10" t="n">
-        <f aca="false">SUM(D5:D6)</f>
-        <v>60</v>
+      <c r="A6" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>900</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="10" t="n">
-        <f aca="false">SUM(D5:D7)</f>
-        <v>960</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <f aca="false">SUM(D8:D8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <f aca="false">SUM(D8:D9)</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <f aca="false">SUM(D8:D10)</f>
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <f aca="false">SUM(D11:D11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <f aca="false">SUM(D11:D12)</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <f aca="false">SUM(D11:D13)</f>
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <f aca="false">SUM(D2:D13)</f>
-        <v>4920</v>
+      <c r="A7" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1585,390 +1721,416 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,0-1)/Settings!$B$6),0)</f>
-        <v>5</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,25-1)/Settings!$B$6),0)</f>
-        <v>7</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,50-1)/Settings!$B$6),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,75-1)/Settings!$B$6),0)</f>
-        <v>11</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,100-1)/Settings!$B$6),0)</f>
-        <v>13</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,125-1)/Settings!$B$6),0)</f>
-        <v>15</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <f aca="false">ROUND($B2*(1+MAX(0,150-1)/Settings!$B$6),0)</f>
-        <v>17</v>
-      </c>
-      <c r="K2" s="12" t="n">
-        <f aca="false">$C2/(Settings!$B$2*Parts!$F$5)</f>
-        <v>0.75</v>
-      </c>
-      <c r="L2" s="12" t="n">
-        <f aca="false">$C2/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M2" s="12" t="n">
-        <f aca="false">$C2/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.09375</v>
+        <v>96</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,0-1)/Settings!$B$6),0)</f>
-        <v>14</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,25-1)/Settings!$B$6),0)</f>
-        <v>20</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,50-1)/Settings!$B$6),0)</f>
-        <v>25</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,75-1)/Settings!$B$6),0)</f>
-        <v>31</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,100-1)/Settings!$B$6),0)</f>
-        <v>37</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,125-1)/Settings!$B$6),0)</f>
-        <v>43</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <f aca="false">ROUND($B3*(1+MAX(0,150-1)/Settings!$B$6),0)</f>
-        <v>49</v>
-      </c>
-      <c r="K3" s="12" t="n">
-        <f aca="false">$C3/(Settings!$B$2*Parts!$F$5)</f>
-        <v>1.25</v>
-      </c>
-      <c r="L3" s="12" t="n">
-        <f aca="false">$C3/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.416666666666667</v>
-      </c>
-      <c r="M3" s="12" t="n">
-        <f aca="false">$C3/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.15625</v>
+        <v>96</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <f aca="false">SUM(D2:D3)</f>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,0-1)/Settings!$B$6),0)</f>
-        <v>40</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,25-1)/Settings!$B$6),0)</f>
-        <v>56</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,50-1)/Settings!$B$6),0)</f>
-        <v>73</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,75-1)/Settings!$B$6),0)</f>
-        <v>89</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,100-1)/Settings!$B$6),0)</f>
-        <v>106</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,125-1)/Settings!$B$6),0)</f>
-        <v>123</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <f aca="false">ROUND($B4*(1+MAX(0,150-1)/Settings!$B$6),0)</f>
-        <v>139</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <f aca="false">$C4/(Settings!$B$2*Parts!$F$5)</f>
-        <v>2</v>
-      </c>
-      <c r="L4" s="12" t="n">
-        <f aca="false">$C4/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="M4" s="12" t="n">
-        <f aca="false">$C4/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.25</v>
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,0-1)/Settings!$B$6),0)</f>
-        <v>95</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,25-1)/Settings!$B$6),0)</f>
-        <v>133</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,50-1)/Settings!$B$6),0)</f>
-        <v>173</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,75-1)/Settings!$B$6),0)</f>
-        <v>212</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,100-1)/Settings!$B$6),0)</f>
-        <v>252</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,125-1)/Settings!$B$6),0)</f>
-        <v>291</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <f aca="false">ROUND($B5*(1+MAX(0,150-1)/Settings!$B$6),0)</f>
-        <v>331</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <f aca="false">$C5/(Settings!$B$2*Parts!$F$5)</f>
-        <v>2.75</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <f aca="false">$C5/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.916666666666667</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <f aca="false">$C5/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.34375</v>
+        <v>102</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <f aca="false">SUM(D5:D5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <f aca="false">SUM(D5:D6)</f>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>93</v>
+      <c r="A7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>900</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <f aca="false">SUM(D5:D7)</f>
+        <v>960</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <f aca="false">$C8/(Settings!$B$2*Parts!$F$5)</f>
-        <v>0.5</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <f aca="false">$C8/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <f aca="false">$C8/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.0625</v>
+        <v>111</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <f aca="false">SUM(D8:D8)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <f aca="false">$C9/(Settings!$B$2*Parts!$F$5)</f>
-        <v>1</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <f aca="false">$C9/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <f aca="false">$C9/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.125</v>
+        <v>111</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <f aca="false">SUM(D8:D9)</f>
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <f aca="false">$C10/(Settings!$B$2*Parts!$F$5)</f>
-        <v>2.25</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <f aca="false">$C10/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.75</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <f aca="false">$C10/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.28125</v>
+        <v>111</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <f aca="false">SUM(D8:D10)</f>
+        <v>1550</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <f aca="false">$C11/(Settings!$B$2*Parts!$F$5)</f>
-        <v>0.75</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <f aca="false">$C11/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <f aca="false">$C11/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.09375</v>
+        <v>117</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <f aca="false">SUM(D11:D11)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <f aca="false">$C12/(Settings!$B$2*Parts!$F$5)</f>
-        <v>0.25</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <f aca="false">$C12/(Settings!$B$2*Parts!$F$6)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <f aca="false">$C12/(Settings!$B$2*Parts!$F$7)</f>
-        <v>0.03125</v>
+        <v>117</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <f aca="false">SUM(D11:D12)</f>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <f aca="false">$C13/(Settings!$B$2*Parts!$F$5)</f>
-        <v>10</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <f aca="false">$C13/(Settings!$B$2*Parts!$F$6)</f>
-        <v>3.33333333333333</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <f aca="false">$C13/(Settings!$B$2*Parts!$F$7)</f>
-        <v>1.25</v>
+        <v>117</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <f aca="false">SUM(D11:D13)</f>
+        <v>1290</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>100</v>
+      <c r="C15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">SUM(D2:D13)</f>
+        <v>4920</v>
       </c>
     </row>
   </sheetData>
@@ -1987,296 +2149,178 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="5" t="n">
-        <f aca="false">Parts!$F$8</f>
-        <v>80</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <f aca="false">Parts!$H$11</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="14" t="n">
-        <f aca="false">B2/(Settings!$B$3*D2)</f>
-        <v>160</v>
-      </c>
-      <c r="F2" s="14" t="n">
-        <f aca="false">B2/(Settings!$B$3*D2+Settings!$B$4)</f>
-        <v>47.0588235294118</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <f aca="false">B2/(2*Settings!$B$3*D2+Settings!$B$4)</f>
-        <v>36.3636363636364</v>
+        <v>74</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="12" t="n">
+        <f aca="false">ROUND(C2*Caves!$C$2*(1+(1-1)/Settings!$B$6),0)</f>
+        <v>5</v>
+      </c>
+      <c r="E2" s="12" t="n">
+        <f aca="false">ROUND(C2*Caves!$C$2*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>7</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <f aca="false">ROUND(C2*Caves!$C$2*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <f aca="false">Parts!$F$8</f>
-        <v>80</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <f aca="false">Parts!$H$12</f>
-        <v>0.8</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <f aca="false">B3/(Settings!$B$3*D3)</f>
-        <v>200</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <f aca="false">B3/(Settings!$B$3*D3+Settings!$B$4)</f>
-        <v>50</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <f aca="false">B3/(2*Settings!$B$3*D3+Settings!$B$4)</f>
-        <v>40</v>
+        <v>74</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <f aca="false">ROUND(C3*Caves!$C$2*(1+(1-1)/Settings!$B$6),0)</f>
+        <v>14</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <f aca="false">ROUND(C3*Caves!$C$2*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>20</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <f aca="false">ROUND(C3*Caves!$C$2*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <f aca="false">Parts!$F$8</f>
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <f aca="false">Parts!$H$13</f>
-        <v>0.55</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <f aca="false">B4/(Settings!$B$3*D4)</f>
-        <v>290.909090909091</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <f aca="false">B4/(Settings!$B$3*D4+Settings!$B$4)</f>
-        <v>54.2372881355932</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <f aca="false">B4/(2*Settings!$B$3*D4+Settings!$B$4)</f>
-        <v>45.7142857142857</v>
+        <v>79</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <f aca="false">ROUND(C4*Caves!$C$3*(1+(1-1)/Settings!$B$6),0)</f>
+        <v>28</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <f aca="false">ROUND(C4*Caves!$C$3*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>39</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <f aca="false">ROUND(C4*Caves!$C$3*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <f aca="false">Parts!$F$9</f>
-        <v>140</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">Parts!$H$11</f>
-        <v>1</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">B5/(Settings!$B$3*D5)</f>
-        <v>280</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <f aca="false">B5/(Settings!$B$3*D5+Settings!$B$4)</f>
-        <v>82.3529411764706</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <f aca="false">B5/(2*Settings!$B$3*D5+Settings!$B$4)</f>
-        <v>63.6363636363636</v>
+        <v>79</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <f aca="false">ROUND(C5*Caves!$C$3*(1+(1-1)/Settings!$B$6),0)</f>
+        <v>80</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <f aca="false">ROUND(C5*Caves!$C$3*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>112</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <f aca="false">ROUND(C5*Caves!$C$3*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <f aca="false">Parts!$F$9</f>
+        <v>83</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <f aca="false">ROUND(C6*Caves!$C$4*(1+(1-1)/Settings!$B$6),0)</f>
         <v>140</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <f aca="false">Parts!$H$12</f>
-        <v>0.8</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">B6/(Settings!$B$3*D6)</f>
-        <v>350</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <f aca="false">B6/(Settings!$B$3*D6+Settings!$B$4)</f>
-        <v>87.5</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <f aca="false">B6/(2*Settings!$B$3*D6+Settings!$B$4)</f>
-        <v>70</v>
+      <c r="E6" s="12" t="n">
+        <f aca="false">ROUND(C6*Caves!$C$4*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>196</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">ROUND(C6*Caves!$C$4*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>264</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <f aca="false">Parts!$F$9</f>
-        <v>140</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <f aca="false">Parts!$H$13</f>
-        <v>0.55</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">B7/(Settings!$B$3*D7)</f>
-        <v>509.090909090909</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <f aca="false">B7/(Settings!$B$3*D7+Settings!$B$4)</f>
-        <v>94.9152542372881</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <f aca="false">B7/(2*Settings!$B$3*D7+Settings!$B$4)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <f aca="false">Parts!$F$10</f>
-        <v>240</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <f aca="false">Parts!$H$11</f>
-        <v>1</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">B8/(Settings!$B$3*D8)</f>
-        <v>480</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <f aca="false">B8/(Settings!$B$3*D8+Settings!$B$4)</f>
-        <v>141.176470588235</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <f aca="false">B8/(2*Settings!$B$3*D8+Settings!$B$4)</f>
-        <v>109.090909090909</v>
+        <v>83</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">ROUND(C7*Caves!$C$4*(1+(1-1)/Settings!$B$6),0)</f>
+        <v>333</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">ROUND(C7*Caves!$C$4*(1+(25-1)/Settings!$B$6),0)</f>
+        <v>465</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <f aca="false">ROUND(C7*Caves!$C$4*(1+(54-1)/Settings!$B$6),0)</f>
+        <v>626</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <f aca="false">Parts!$F$10</f>
-        <v>240</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <f aca="false">Parts!$H$12</f>
-        <v>0.8</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <f aca="false">B9/(Settings!$B$3*D9)</f>
-        <v>600</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <f aca="false">B9/(Settings!$B$3*D9+Settings!$B$4)</f>
-        <v>150</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <f aca="false">B9/(2*Settings!$B$3*D9+Settings!$B$4)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <f aca="false">Parts!$F$10</f>
-        <v>240</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <f aca="false">Parts!$H$13</f>
-        <v>0.55</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">B10/(Settings!$B$3*D10)</f>
-        <v>872.727272727273</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <f aca="false">B10/(Settings!$B$3*D10+Settings!$B$4)</f>
-        <v>162.71186440678</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <f aca="false">B10/(2*Settings!$B$3*D10+Settings!$B$4)</f>
-        <v>137.142857142857</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>104</v>
+      <c r="A9" s="7" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2295,187 +2339,361 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
-        <f aca="false">A2*Settings!$B$8</f>
-        <v>25</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <f aca="false">Settings!$B$7-1+B2</f>
-        <v>28</v>
-      </c>
       <c r="D2" s="15" t="n">
-        <f aca="false">ROUND(Settings!$B$9*Settings!$B$10^(A2-1),0)</f>
-        <v>80</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <f aca="false">SUM($D$2:D2)</f>
-        <v>80</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <f aca="false">Settings!$B$8</f>
-        <v>25</v>
+        <f aca="false">IF($C2&gt;1,"—",$B2/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <f aca="false">IF($C2&gt;2,"—",$B2/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <f aca="false">IF($C2&gt;3,"—",$B2/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <f aca="false">A3*Settings!$B$8</f>
-        <v>50</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <f aca="false">Settings!$B$7-1+B3</f>
-        <v>53</v>
+      <c r="A3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D3" s="15" t="n">
-        <f aca="false">ROUND(Settings!$B$9*Settings!$B$10^(A3-1),0)</f>
-        <v>128</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <f aca="false">SUM($D$2:D3)</f>
-        <v>208</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <f aca="false">Settings!$B$8</f>
-        <v>25</v>
+        <f aca="false">IF($C3&gt;1,"—",$B3/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <f aca="false">IF($C3&gt;2,"—",$B3/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <f aca="false">IF($C3&gt;3,"—",$B3/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <f aca="false">IF($C4&gt;1,"—",$B4/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1.25</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <f aca="false">IF($C4&gt;2,"—",$B4/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <f aca="false">IF($C4&gt;3,"—",$B4/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <f aca="false">IF($C5&gt;1,"—",$B5/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.25</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <f aca="false">IF($C5&gt;2,"—",$B5/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <f aca="false">IF($C5&gt;3,"—",$B5/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.28125</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <f aca="false">A4*Settings!$B$8</f>
-        <v>75</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <f aca="false">Settings!$B$7-1+B4</f>
-        <v>78</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <f aca="false">ROUND(Settings!$B$9*Settings!$B$10^(A4-1),0)</f>
-        <v>205</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <f aca="false">SUM($D$2:D4)</f>
-        <v>413</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <f aca="false">Settings!$B$8</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <f aca="false">A5*Settings!$B$8</f>
-        <v>100</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <f aca="false">Settings!$B$7-1+B5</f>
-        <v>103</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <f aca="false">ROUND(Settings!$B$9*Settings!$B$10^(A5-1),0)</f>
-        <v>328</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <f aca="false">SUM($D$2:D5)</f>
-        <v>741</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <f aca="false">Settings!$B$8</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <f aca="false">A6*Settings!$B$8</f>
-        <v>125</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <f aca="false">Settings!$B$7-1+B6</f>
-        <v>128</v>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D6" s="15" t="n">
-        <f aca="false">ROUND(Settings!$B$9*Settings!$B$10^(A6-1),0)</f>
-        <v>524</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <f aca="false">SUM($D$2:D6)</f>
-        <v>1265</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <f aca="false">Settings!$B$8</f>
-        <v>25</v>
+        <f aca="false">IF($C6&gt;1,"—",$B6/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <f aca="false">IF($C6&gt;2,"—",$B6/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">IF($C6&gt;3,"—",$B6/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.09375</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <f aca="false">IF($C7&gt;1,"—",$B7/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <f aca="false">IF($C7&gt;2,"—",$B7/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <f aca="false">IF($C7&gt;3,"—",$B7/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <f aca="false">Settings!$B$11-Settings!$B$7+1</f>
-        <v>153</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <f aca="false">Settings!$B$11</f>
-        <v>156</v>
+      <c r="A8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <f aca="false">IF($C8&gt;1,"—",$B8/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <f aca="false">IF($C8&gt;2,"—",$B8/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <f aca="false">IF($C8&gt;3,"—",$B8/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <f aca="false">B8-B6</f>
-        <v>28</v>
+        <v>130</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <f aca="false">IF($C9&gt;1,"—",$B9/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1.25</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <f aca="false">IF($C9&gt;2,"—",$B9/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <f aca="false">IF($C9&gt;3,"—",$B9/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <f aca="false">IF($C10&gt;1,"—",$B10/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <f aca="false">IF($C10&gt;2,"—",$B10/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <f aca="false">IF($C10&gt;3,"—",$B10/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>112</v>
+      <c r="A11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <f aca="false">IF($C11&gt;1,"—",$B11/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.75</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <f aca="false">IF($C11&gt;2,"—",$B11/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <f aca="false">IF($C11&gt;3,"—",$B11/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <f aca="false">IF($C12&gt;1,"—",$B12/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <f aca="false">IF($C12&gt;2,"—",$B12/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <f aca="false">IF($C12&gt;3,"—",$B12/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="15" t="str">
+        <f aca="false">IF($C13&gt;1,"—",$B13/(Settings!$B$2*Parts!$F$5))</f>
+        <v>—</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <f aca="false">IF($C13&gt;2,"—",$B13/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <f aca="false">IF($C13&gt;3,"—",$B13/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="15" t="str">
+        <f aca="false">IF($C14&gt;1,"—",$B14/(Settings!$B$2*Parts!$F$5))</f>
+        <v>—</v>
+      </c>
+      <c r="E14" s="15" t="str">
+        <f aca="false">IF($C14&gt;2,"—",$B14/(Settings!$B$2*Parts!$F$6))</f>
+        <v>—</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <f aca="false">IF($C14&gt;3,"—",$B14/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">IF($C15&gt;1,"—",$B15/(Settings!$B$2*Parts!$F$5))</f>
+        <v>10</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">IF($C15&gt;2,"—",$B15/(Settings!$B$2*Parts!$F$6))</f>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">IF($C15&gt;3,"—",$B15/(Settings!$B$2*Parts!$F$7))</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2494,29 +2712,539 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <f aca="false">Parts!$F$8</f>
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <f aca="false">Parts!$H$11</f>
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <f aca="false">B2/(Settings!$B$3*D2)</f>
+        <v>160</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <f aca="false">B2/(Settings!$B$3*D2+Settings!$B$4)</f>
+        <v>47.0588235294118</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <f aca="false">B2/(2*Settings!$B$3*D2+Settings!$B$4)</f>
+        <v>36.3636363636364</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <f aca="false">Parts!$F$8</f>
+        <v>80</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <f aca="false">Parts!$H$12</f>
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <f aca="false">B3/(Settings!$B$3*D3)</f>
+        <v>200</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <f aca="false">B3/(Settings!$B$3*D3+Settings!$B$4)</f>
+        <v>50</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <f aca="false">B3/(2*Settings!$B$3*D3+Settings!$B$4)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <f aca="false">Parts!$F$8</f>
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <f aca="false">Parts!$H$13</f>
+        <v>0.55</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <f aca="false">B4/(Settings!$B$3*D4)</f>
+        <v>290.909090909091</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <f aca="false">B4/(Settings!$B$3*D4+Settings!$B$4)</f>
+        <v>54.2372881355932</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <f aca="false">B4/(2*Settings!$B$3*D4+Settings!$B$4)</f>
+        <v>45.7142857142857</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <f aca="false">Parts!$F$9</f>
+        <v>140</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">Parts!$H$11</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <f aca="false">B5/(Settings!$B$3*D5)</f>
+        <v>280</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <f aca="false">B5/(Settings!$B$3*D5+Settings!$B$4)</f>
+        <v>82.3529411764706</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <f aca="false">B5/(2*Settings!$B$3*D5+Settings!$B$4)</f>
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <f aca="false">Parts!$F$9</f>
+        <v>140</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">Parts!$H$12</f>
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <f aca="false">B6/(Settings!$B$3*D6)</f>
+        <v>350</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <f aca="false">B6/(Settings!$B$3*D6+Settings!$B$4)</f>
+        <v>87.5</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <f aca="false">B6/(2*Settings!$B$3*D6+Settings!$B$4)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <f aca="false">Parts!$F$9</f>
+        <v>140</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">Parts!$H$13</f>
+        <v>0.55</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <f aca="false">B7/(Settings!$B$3*D7)</f>
+        <v>509.090909090909</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <f aca="false">B7/(Settings!$B$3*D7+Settings!$B$4)</f>
+        <v>94.9152542372881</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <f aca="false">B7/(2*Settings!$B$3*D7+Settings!$B$4)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <f aca="false">Parts!$F$10</f>
+        <v>240</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">Parts!$H$11</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <f aca="false">B8/(Settings!$B$3*D8)</f>
+        <v>480</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <f aca="false">B8/(Settings!$B$3*D8+Settings!$B$4)</f>
+        <v>141.176470588235</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <f aca="false">B8/(2*Settings!$B$3*D8+Settings!$B$4)</f>
+        <v>109.090909090909</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <f aca="false">Parts!$F$10</f>
+        <v>240</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">Parts!$H$12</f>
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <f aca="false">B9/(Settings!$B$3*D9)</f>
+        <v>600</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <f aca="false">B9/(Settings!$B$3*D9+Settings!$B$4)</f>
+        <v>150</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <f aca="false">B9/(2*Settings!$B$3*D9+Settings!$B$4)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <f aca="false">Parts!$F$10</f>
+        <v>240</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">Parts!$H$13</f>
+        <v>0.55</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <f aca="false">B10/(Settings!$B$3*D10)</f>
+        <v>872.727272727273</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <f aca="false">B10/(Settings!$B$3*D10+Settings!$B$4)</f>
+        <v>162.71186440678</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <f aca="false">B10/(2*Settings!$B$3*D10+Settings!$B$4)</f>
+        <v>137.142857142857</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f aca="false">Parts!D6</f>
+        <v>60</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <f aca="false">SUM($C$2:C2)-SUM($B$2:B2)</f>
+        <v>-60</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <f aca="false">Caves!O2</f>
+        <v>80</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <f aca="false">SUM($C$2:C3)-SUM($B$2:B3)</f>
+        <v>-140</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <f aca="false">Caves!N2</f>
+        <v>300</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <f aca="false">SUM($C$2:C4)-SUM($B$2:B4)</f>
+        <v>160</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <f aca="false">Parts!D3</f>
+        <v>120</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <f aca="false">SUM($C$2:C5)-SUM($B$2:B5)</f>
+        <v>40</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <f aca="false">Parts!D9</f>
+        <v>150</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">SUM($C$2:C6)-SUM($B$2:B6)</f>
+        <v>-110</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <f aca="false">Caves!O3</f>
+        <v>200</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">SUM($C$2:C7)-SUM($B$2:B7)</f>
+        <v>-310</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <f aca="false">Caves!N3</f>
+        <v>800</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <f aca="false">SUM($C$2:C8)-SUM($B$2:B8)</f>
+        <v>490</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <f aca="false">Parts!D7</f>
+        <v>900</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <f aca="false">SUM($C$2:C9)-SUM($B$2:B9)</f>
+        <v>-410</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <f aca="false">Caves!O4</f>
+        <v>500</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <f aca="false">SUM($C$2:C10)-SUM($B$2:B10)</f>
+        <v>-910</v>
+      </c>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <f aca="false">Caves!N4</f>
+        <v>2000</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <f aca="false">SUM($C$2:C11)-SUM($B$2:B11)</f>
+        <v>1090</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1.4</v>
@@ -2524,7 +3252,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>0.3</v>
@@ -2532,7 +3260,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
@@ -2540,7 +3268,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>0.12</v>
@@ -2548,7 +3276,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>5</v>
@@ -2556,7 +3284,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>0.08</v>
@@ -2564,7 +3292,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>120</v>
@@ -2572,7 +3300,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1.8</v>
@@ -2580,49 +3308,49 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A12-1))</f>
         <v>1.4</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A12-1))</f>
         <v>2</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="13" t="n">
         <f aca="false">C12*(1+$B$5*($B$6-1))/B12*60</f>
         <v>126.857142857143</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">$B$7*A12</f>
         <v>0.08</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -2632,27 +3360,27 @@
       <c r="A13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A13-1))</f>
         <v>1.07692307692308</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A13-1))</f>
         <v>3</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="13" t="n">
         <f aca="false">C13*(1+$B$5*($B$6-1))/B13*60</f>
         <v>247.371428571429</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="21" t="n">
         <f aca="false">$B$7*A13</f>
         <v>0.16</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A13-2),0)</f>
         <v>120</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="13" t="n">
         <f aca="false">G12+F13</f>
         <v>120</v>
       </c>
@@ -2661,27 +3389,27 @@
       <c r="A14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A14-1))</f>
         <v>0.875</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A14-1))</f>
         <v>4</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="13" t="n">
         <f aca="false">C14*(1+$B$5*($B$6-1))/B14*60</f>
         <v>405.942857142857</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">$B$7*A14</f>
         <v>0.24</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A14-2),0)</f>
         <v>216</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="13" t="n">
         <f aca="false">G13+F14</f>
         <v>336</v>
       </c>
@@ -2690,27 +3418,27 @@
       <c r="A15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A15-1))</f>
         <v>0.736842105263158</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A15-1))</f>
         <v>5</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="13" t="n">
         <f aca="false">C15*(1+$B$5*($B$6-1))/B15*60</f>
         <v>602.571428571429</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">$B$7*A15</f>
         <v>0.32</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A15-2),0)</f>
         <v>389</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">G14+F15</f>
         <v>725</v>
       </c>
@@ -2719,27 +3447,27 @@
       <c r="A16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A16-1))</f>
         <v>0.636363636363636</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A16-1))</f>
         <v>6</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">C16*(1+$B$5*($B$6-1))/B16*60</f>
         <v>837.257142857143</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">$B$7*A16</f>
         <v>0.4</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A16-2),0)</f>
         <v>700</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="13" t="n">
         <f aca="false">G15+F16</f>
         <v>1425</v>
       </c>
@@ -2748,27 +3476,27 @@
       <c r="A17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A17-1))</f>
         <v>0.56</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A17-1))</f>
         <v>7</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="13" t="n">
         <f aca="false">C17*(1+$B$5*($B$6-1))/B17*60</f>
         <v>1110</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="21" t="n">
         <f aca="false">$B$7*A17</f>
         <v>0.48</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A17-2),0)</f>
         <v>1260</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="13" t="n">
         <f aca="false">G16+F17</f>
         <v>2685</v>
       </c>
@@ -2777,27 +3505,27 @@
       <c r="A18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A18-1))</f>
         <v>0.5</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A18-1))</f>
         <v>8</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="13" t="n">
         <f aca="false">C18*(1+$B$5*($B$6-1))/B18*60</f>
         <v>1420.8</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="21" t="n">
         <f aca="false">$B$7*A18</f>
         <v>0.56</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A18-2),0)</f>
         <v>2267</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="13" t="n">
         <f aca="false">G17+F18</f>
         <v>4952</v>
       </c>
@@ -2806,27 +3534,27 @@
       <c r="A19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A19-1))</f>
         <v>0.451612903225806</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A19-1))</f>
         <v>9</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="13" t="n">
         <f aca="false">C19*(1+$B$5*($B$6-1))/B19*60</f>
         <v>1769.65714285714</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="21" t="n">
         <f aca="false">$B$7*A19</f>
         <v>0.64</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A19-2),0)</f>
         <v>4081</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">G18+F19</f>
         <v>9033</v>
       </c>
@@ -2835,27 +3563,27 @@
       <c r="A20" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A20-1))</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A20-1))</f>
         <v>10</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="13" t="n">
         <f aca="false">C20*(1+$B$5*($B$6-1))/B20*60</f>
         <v>2156.57142857143</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="21" t="n">
         <f aca="false">$B$7*A20</f>
         <v>0.72</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A20-2),0)</f>
         <v>7347</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="13" t="n">
         <f aca="false">G19+F20</f>
         <v>16380</v>
       </c>
@@ -2864,34 +3592,29 @@
       <c r="A21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="19" t="n">
         <f aca="false">$B$2/(1+$B$3*(A21-1))</f>
         <v>0.378378378378378</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="20" t="n">
         <f aca="false">$B$4*(1+0.5*(A21-1))</f>
         <v>11</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="13" t="n">
         <f aca="false">C21*(1+$B$5*($B$6-1))/B21*60</f>
         <v>2581.54285714286</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="21" t="n">
         <f aca="false">$B$7*A21</f>
         <v>0.8</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="13" t="n">
         <f aca="false">ROUND($B$8*$B$9^(A21-2),0)</f>
         <v>13224</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="13" t="n">
         <f aca="false">G20+F21</f>
         <v>29604</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -12,11 +12,12 @@
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Caves" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Parts" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Ore" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Dig times" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Battery" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Progress" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Pet" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Block coins" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Materials" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Mods" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Dig times" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Battery" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Progress" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="194">
-  <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.7)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="234">
+  <si>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.8)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -54,16 +55,22 @@
     <t xml:space="preserve">Tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Settings – shared numbers (dig rate, battery, conveyor, bridges, caches, depth bonus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caves – the three caves: ore and hard-rock chances, value multiplier, relic, outpost, bridge and cache payouts</t>
+    <t xml:space="preserve">Settings – shared numbers (dig rate, battery, conveyor, caches, Flux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caves – the three caves: ore and hard-rock chances, coin multiplier, relic, outpost, bridge and cache payouts</t>
   </si>
   <si>
     <t xml:space="preserve">Parts – every part, its cost and stats, and the total cost to max each slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Ore – what each ore sells for at the start, outpost and end of each cave</t>
+    <t xml:space="preserve">Block coins – coins for digging each block in each cave, and coins per second with each arm tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materials – forge recipes: ore needed, refine time, and whether refining beats selling the ore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mods – every computer mod: shape, build cost, Flux to upgrade and how long the nano-bot takes to make it</t>
   </si>
   <si>
     <t xml:space="preserve">Dig times – seconds to break each block with each arm tier ("—" = too hard for that tier)</t>
@@ -75,7 +82,7 @@
     <t xml:space="preserve">Progress – a rough cost path through the three caves</t>
   </si>
   <si>
-    <t xml:space="preserve">Pet – Pip the Mole: earnings and training cost per level</t>
+    <t xml:space="preserve">Ore prices are fixed per type in v0.8 (no depth bonus); the shop buys ore and materials from storage.</t>
   </si>
   <si>
     <t xml:space="preserve">Setting</t>
@@ -111,12 +118,6 @@
     <t xml:space="preserve">Battery per second at base or an outpost (CHARGE_RATE)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ore depth bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ore is worth +100% for every this many blocks of depth (ORE_DEPTH_BONUS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Outpost depth (m)</t>
   </si>
   <si>
@@ -195,13 +196,37 @@
     <t xml:space="preserve">Share of ore lost in a cave-in (ROCK.cargoLoss)</t>
   </si>
   <si>
+    <t xml:space="preserve">Flux per minute (per bot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux each nano-bot makes per minute (NANOBOT.fluxPerMin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offline cap (hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux stops building up after this long away (NANOBOT.offlineCapHours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade to Lv 2 (Flux per cell)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux per cell of the mod's shape (COMPUTER.upgradeFlux[0])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade to Lv 3 (Flux per cell)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux per cell of the mod's shape (COMPUTER.upgradeFlux[1])</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cave</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Ore value ×</t>
+    <t xml:space="preserve">Coin multiplier</t>
   </si>
   <si>
     <t xml:space="preserve">Ore 1</t>
@@ -402,19 +427,73 @@
     <t xml:space="preserve">Total to max every part</t>
   </si>
   <si>
+    <t xml:space="preserve">Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins (base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness (hp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unstable rock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore (plus the ore itself)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins per second while tunnelling through each cave's main rock (no walking time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave rock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins per block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dirt / clay (cave 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone (cave 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basalt (cave 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Prospector mod adds 10–30% to every block. Caches, relics and selling ore come on top.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ore</t>
   </si>
   <si>
-    <t xml:space="preserve">Base value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the mouth (1 m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the outpost (25 m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At the relic (54 m)</t>
+    <t xml:space="preserve">Sells for</t>
   </si>
   <si>
     <t xml:space="preserve">Copper</t>
@@ -429,13 +508,124 @@
     <t xml:space="preserve">Crystal</t>
   </si>
   <si>
-    <t xml:space="preserve">Value = base value × cave multiplier × (1 + depth ÷ ore depth bonus). Caches pay in the cave's best (second) ore.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness (hp)</t>
+    <t xml:space="preserve">Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refine time (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore value used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit vs selling the ore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conductors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refining is mostly for building mods; selling a material pays a little more than selling its ore. Refine times are short while testing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build cost in coins (materials at sell price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux to Lv 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux to Lv 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutes of Flux (1 bot) to max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fits the starting computer?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drill Chip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Saver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prospector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamp Chip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardrock Driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■■</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (fills the passive row)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolant Loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ / ■ (tall)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (needs an expansion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore Sense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overclock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting computer: 2×2. The top row (2 cells) is passive; the bottom row is for active skills and opens after Town 1. Shapes are fixed (no rotating).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamp Chip and Ore Sense levels are in blocks; the rest are percentages.</t>
   </si>
   <si>
     <t xml:space="preserve">Needs arms tier</t>
@@ -450,34 +640,13 @@
     <t xml:space="preserve">Plasma Cutters (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dirt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unstable rock</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rubble</t>
   </si>
   <si>
     <t xml:space="preserve">Treasure cache</t>
   </si>
   <si>
-    <t xml:space="preserve">Granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignores the pet bonus (+8% dig power per pet level). Relics in caves 2 and 3 are sealed in granite / obsidian, so you need that tier to reach them.</t>
+    <t xml:space="preserve">Without mods (Drill Chip and Overclock add dig speed; Hardrock Driver speeds up granite and obsidian). Relics in caves 2 and 3 are sealed in granite / obsidian, so you need that tier to reach them.</t>
   </si>
   <si>
     <t xml:space="preserve">Blocks you can walk</t>
@@ -558,74 +727,27 @@
     <t xml:space="preserve">Cave 3: Core Heart</t>
   </si>
   <si>
-    <t xml:space="preserve">End of v0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending only (ore income not counted). A negative running total is the ore you need to earn by digging before that step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seconds per block at level 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig speed per level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coins per block at level 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ore chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ore multiplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dig bonus to walker per level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First training cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training cost growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seconds per block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coins per block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coins per minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walker dig bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost to train to this level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hatched from the fossil (cave 1)</t>
+    <t xml:space="preserve">End of v0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relic rewards only. A negative running total is what you need to earn from block coins, caches and selling ore before that step (see Block coins). Mods are extra.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="0.0\×"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
-    <numFmt numFmtId="169" formatCode="0.00"/>
-    <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0;\(#,##0\);0"/>
+    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="172" formatCode="0.00"/>
+    <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -686,17 +808,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <i val="true"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF666666"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -750,7 +872,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -775,12 +897,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -811,11 +933,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -827,15 +945,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1091,7 +1209,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1181,6 +1299,219 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f aca="false">Parts!D6</f>
+        <v>60</v>
+      </c>
+      <c r="D2" s="20" t="n">
+        <f aca="false">SUM($C$2:C2)-SUM($B$2:B2)</f>
+        <v>-60</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <f aca="false">Caves!O2</f>
+        <v>80</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <f aca="false">SUM($C$2:C3)-SUM($B$2:B3)</f>
+        <v>-140</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <f aca="false">Caves!N2</f>
+        <v>300</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <f aca="false">SUM($C$2:C4)-SUM($B$2:B4)</f>
+        <v>160</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <f aca="false">Parts!D3</f>
+        <v>120</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <f aca="false">SUM($C$2:C5)-SUM($B$2:B5)</f>
+        <v>40</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <f aca="false">Parts!D9</f>
+        <v>150</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <f aca="false">SUM($C$2:C6)-SUM($B$2:B6)</f>
+        <v>-110</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <f aca="false">Caves!O3</f>
+        <v>200</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <f aca="false">SUM($C$2:C7)-SUM($B$2:B7)</f>
+        <v>-310</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <f aca="false">Caves!N3</f>
+        <v>800</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <f aca="false">SUM($C$2:C8)-SUM($B$2:B8)</f>
+        <v>490</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <f aca="false">Parts!D7</f>
+        <v>900</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <f aca="false">SUM($C$2:C9)-SUM($B$2:B9)</f>
+        <v>-410</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <f aca="false">Caves!O4</f>
+        <v>500</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <f aca="false">SUM($C$2:C10)-SUM($B$2:B10)</f>
+        <v>-910</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <f aca="false">Caves!N4</f>
+        <v>2000</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <f aca="false">SUM($C$2:C11)-SUM($B$2:B11)</f>
+        <v>1090</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1530,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -1208,212 +1539,245 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>20</v>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
+      <c r="C3" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>24</v>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>26</v>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>30</v>
+        <v>80</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>32</v>
+        <v>2.5</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>36</v>
+        <v>160</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
+        <v>2</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>48</v>
+        <v>1.8</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>52</v>
+        <v>0.3</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1451,62 +1815,62 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>73</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1514,19 +1878,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>0.025</v>
@@ -1547,28 +1911,28 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N2" s="11" t="n">
         <v>300</v>
       </c>
       <c r="O2" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A2-1),0)</f>
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A2-1),0)</f>
         <v>80</v>
       </c>
       <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="R2" s="12" t="n">
         <f aca="false">ROUND(Settings!$B$10*C2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="R2" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$11*C2,0)</f>
         <v>160</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1576,19 +1940,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>0.03</v>
@@ -1609,28 +1973,28 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="N3" s="11" t="n">
         <v>800</v>
       </c>
       <c r="O3" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A3-1),0)</f>
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A3-1),0)</f>
         <v>200</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q3" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C3,0)</f>
+        <v>90</v>
+      </c>
+      <c r="R3" s="12" t="n">
         <f aca="false">ROUND(Settings!$B$10*C3,0)</f>
-        <v>120</v>
-      </c>
-      <c r="R3" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$11*C3,0)</f>
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1638,19 +2002,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>0.025</v>
@@ -1671,38 +2035,38 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="N4" s="11" t="n">
         <v>2000</v>
       </c>
       <c r="O4" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$8*Settings!$B$9^(A4-1),0)</f>
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A4-1),0)</f>
         <v>500</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C4,0)</f>
+        <v>120</v>
+      </c>
+      <c r="R4" s="12" t="n">
         <f aca="false">ROUND(Settings!$B$10*C4,0)</f>
-        <v>210</v>
-      </c>
-      <c r="R4" s="12" t="n">
-        <f aca="false">ROUND(Settings!$B$11*C4,0)</f>
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>87</v>
+      <c r="A6" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>88</v>
+      <c r="A7" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1736,55 +2100,55 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>95</v>
+      <c r="A1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -1796,25 +2160,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>3</v>
@@ -1826,25 +2190,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -1856,28 +2220,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">SUM(D5:D5)</f>
@@ -1886,28 +2250,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">SUM(D5:D6)</f>
@@ -1916,28 +2280,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>900</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -1946,25 +2310,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -1976,25 +2340,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>16</v>
@@ -2006,25 +2370,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>240</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>30</v>
@@ -2036,25 +2400,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
@@ -2066,25 +2430,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.8</v>
@@ -2096,25 +2460,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.55</v>
@@ -2126,7 +2490,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">SUM(D2:D13)</f>
@@ -2149,178 +2513,308 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>128</v>
+      <c r="A1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" s="12" t="n">
-        <f aca="false">ROUND(C2*Caves!$C$2*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>5</v>
-      </c>
-      <c r="E2" s="12" t="n">
-        <f aca="false">ROUND(C2*Caves!$C$2*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>7</v>
-      </c>
-      <c r="F2" s="12" t="n">
-        <f aca="false">ROUND(C2*Caves!$C$2*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>9</v>
+        <v>138</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B2*Caves!$C$2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B2*Caves!$C$3,0))</f>
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B2*Caves!$C$4,0))</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D3" s="12" t="n">
-        <f aca="false">ROUND(C3*Caves!$C$2*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>14</v>
-      </c>
-      <c r="E3" s="12" t="n">
-        <f aca="false">ROUND(C3*Caves!$C$2*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>20</v>
-      </c>
-      <c r="F3" s="12" t="n">
-        <f aca="false">ROUND(C3*Caves!$C$2*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>26</v>
+        <v>139</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B3*Caves!$C$2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B3*Caves!$C$3,0))</f>
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B3*Caves!$C$4,0))</f>
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <f aca="false">ROUND(C4*Caves!$C$3*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>28</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <f aca="false">ROUND(C4*Caves!$C$3*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>39</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <f aca="false">ROUND(C4*Caves!$C$3*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>53</v>
+        <v>140</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B4*Caves!$C$2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B4*Caves!$C$3,0))</f>
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B4*Caves!$C$4,0))</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <f aca="false">ROUND(C5*Caves!$C$3*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>80</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <f aca="false">ROUND(C5*Caves!$C$3*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>112</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <f aca="false">ROUND(C5*Caves!$C$3*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>151</v>
+        <v>141</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B5*Caves!$C$2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B5*Caves!$C$3,0))</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B5*Caves!$C$4,0))</f>
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <f aca="false">ROUND(C6*Caves!$C$4*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>140</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <f aca="false">ROUND(C6*Caves!$C$4*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>196</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <f aca="false">ROUND(C6*Caves!$C$4*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>264</v>
+        <v>142</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B6*Caves!$C$2,0))</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B6*Caves!$C$3,0))</f>
+        <v>6</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B6*Caves!$C$4,0))</f>
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <f aca="false">ROUND(C7*Caves!$C$4*(1+(1-1)/Settings!$B$6),0)</f>
-        <v>333</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <f aca="false">ROUND(C7*Caves!$C$4*(1+(25-1)/Settings!$B$6),0)</f>
-        <v>465</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <f aca="false">ROUND(C7*Caves!$C$4*(1+(54-1)/Settings!$B$6),0)</f>
-        <v>626</v>
+        <v>143</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B7*Caves!$C$2,0))</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B7*Caves!$C$3,0))</f>
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B7*Caves!$C$4,0))</f>
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B8*Caves!$C$2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B8*Caves!$C$3,0))</f>
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B8*Caves!$C$4,0))</f>
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>133</v>
+      <c r="A9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B9*Caves!$C$2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B9*Caves!$C$3,0))</f>
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <f aca="false">MAX(1,ROUND(B9*Caves!$C$4,0))</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <f aca="false">C2</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">B13/(F2/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <f aca="false">B13/(F2/(Settings!$B$2*Parts!$F$6))</f>
+        <v>6</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <f aca="false">B13/(F2/(Settings!$B$2*Parts!$F$7))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <f aca="false">D4</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <f aca="false">B14/(F4/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.4</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <f aca="false">B14/(F4/(Settings!$B$2*Parts!$F$6))</f>
+        <v>7.2</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <f aca="false">B14/(F4/(Settings!$B$2*Parts!$F$7))</f>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <f aca="false">E5</f>
+        <v>6</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">B15/(F5/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.66666666666667</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">B15/(F5/(Settings!$B$2*Parts!$F$6))</f>
+        <v>8</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">B15/(F5/(Settings!$B$2*Parts!$F$7))</f>
+        <v>21.3333333333333</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2339,361 +2833,213 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>139</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="n">
-        <f aca="false">IF($C2&gt;1,"—",$B2/(Settings!$B$2*Parts!$F$5))</f>
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <f aca="false">IF($C2&gt;2,"—",$B2/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="F2" s="15" t="n">
-        <f aca="false">IF($C2&gt;3,"—",$B2/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.0625</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15" t="n">
-        <f aca="false">IF($C3&gt;1,"—",$B3/(Settings!$B$2*Parts!$F$5))</f>
-        <v>1</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <f aca="false">IF($C3&gt;2,"—",$B3/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <f aca="false">IF($C3&gt;3,"—",$B3/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <f aca="false">IF($C4&gt;1,"—",$B4/(Settings!$B$2*Parts!$F$5))</f>
-        <v>1.25</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <f aca="false">IF($C4&gt;2,"—",$B4/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.416666666666667</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <f aca="false">IF($C4&gt;3,"—",$B4/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.15625</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <f aca="false">IF($C5&gt;1,"—",$B5/(Settings!$B$2*Parts!$F$5))</f>
-        <v>2.25</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <f aca="false">IF($C5&gt;2,"—",$B5/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.75</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <f aca="false">IF($C5&gt;3,"—",$B5/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.28125</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <f aca="false">IF($C6&gt;1,"—",$B6/(Settings!$B$2*Parts!$F$5))</f>
-        <v>0.75</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <f aca="false">IF($C6&gt;2,"—",$B6/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <f aca="false">IF($C6&gt;3,"—",$B6/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.09375</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <f aca="false">IF($C7&gt;1,"—",$B7/(Settings!$B$2*Parts!$F$5))</f>
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <f aca="false">IF($C7&gt;2,"—",$B7/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <f aca="false">IF($C7&gt;3,"—",$B7/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.03125</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <f aca="false">IF($C8&gt;1,"—",$B8/(Settings!$B$2*Parts!$F$5))</f>
-        <v>0.75</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <f aca="false">IF($C8&gt;2,"—",$B8/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <f aca="false">IF($C8&gt;3,"—",$B8/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.09375</v>
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <f aca="false">B8*$B$2+C8*$B$3+D8*$B$4+E8*$B$5</f>
+        <v>12</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <f aca="false">G8-H8</f>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <f aca="false">IF($C9&gt;1,"—",$B9/(Settings!$B$2*Parts!$F$5))</f>
-        <v>1.25</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">IF($C9&gt;2,"—",$B9/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.416666666666667</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <f aca="false">IF($C9&gt;3,"—",$B9/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.15625</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <f aca="false">B9*$B$2+C9*$B$3+D9*$B$4+E9*$B$5</f>
+        <v>38</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <f aca="false">G9-H9</f>
+        <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="15" t="n">
-        <f aca="false">IF($C10&gt;1,"—",$B10/(Settings!$B$2*Parts!$F$5))</f>
+      <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">IF($C10&gt;2,"—",$B10/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <f aca="false">IF($C10&gt;3,"—",$B10/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.25</v>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <f aca="false">B10*$B$2+C10*$B$3+D10*$B$4+E10*$B$5</f>
+        <v>106</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <f aca="false">G10-H10</f>
+        <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <f aca="false">IF($C11&gt;1,"—",$B11/(Settings!$B$2*Parts!$F$5))</f>
-        <v>2.75</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">IF($C11&gt;2,"—",$B11/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.916666666666667</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <f aca="false">IF($C11&gt;3,"—",$B11/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.34375</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <f aca="false">IF($C12&gt;1,"—",$B12/(Settings!$B$2*Parts!$F$5))</f>
-        <v>1</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <f aca="false">IF($C12&gt;2,"—",$B12/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <f aca="false">IF($C12&gt;3,"—",$B12/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.125</v>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <f aca="false">B11*$B$2+C11*$B$3+D11*$B$4+E11*$B$5</f>
+        <v>265</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <f aca="false">G11-H11</f>
+        <v>55</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="15" t="str">
-        <f aca="false">IF($C13&gt;1,"—",$B13/(Settings!$B$2*Parts!$F$5))</f>
-        <v>—</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <f aca="false">IF($C13&gt;2,"—",$B13/(Settings!$B$2*Parts!$F$6))</f>
-        <v>0.833333333333333</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <f aca="false">IF($C13&gt;3,"—",$B13/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.3125</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="15" t="str">
-        <f aca="false">IF($C14&gt;1,"—",$B14/(Settings!$B$2*Parts!$F$5))</f>
-        <v>—</v>
-      </c>
-      <c r="E14" s="15" t="str">
-        <f aca="false">IF($C14&gt;2,"—",$B14/(Settings!$B$2*Parts!$F$6))</f>
-        <v>—</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <f aca="false">IF($C14&gt;3,"—",$B14/(Settings!$B$2*Parts!$F$7))</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <f aca="false">IF($C15&gt;1,"—",$B15/(Settings!$B$2*Parts!$F$5))</f>
-        <v>10</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <f aca="false">IF($C15&gt;2,"—",$B15/(Settings!$B$2*Parts!$F$6))</f>
-        <v>3.33333333333333</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <f aca="false">IF($C15&gt;3,"—",$B15/(Settings!$B$2*Parts!$F$7))</f>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>149</v>
+      <c r="A13" s="6" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2708,6 +3054,957 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <f aca="false">H2+D2*Materials!$G$8+E2*Materials!$G$9+F2*Materials!$G$10+G2*Materials!$G$11</f>
+        <v>72</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <f aca="false">C2*Settings!$B$21</f>
+        <v>25</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <f aca="false">C2*Settings!$B$22</f>
+        <v>75</v>
+      </c>
+      <c r="L2" s="17" t="n">
+        <f aca="false">(J2+K2)/Settings!$B$19</f>
+        <v>10</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <f aca="false">H3+D3*Materials!$G$8+E3*Materials!$G$9+F3*Materials!$G$10+G3*Materials!$G$11</f>
+        <v>108</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <f aca="false">C3*Settings!$B$21</f>
+        <v>25</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <f aca="false">C3*Settings!$B$22</f>
+        <v>75</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <f aca="false">(J3+K3)/Settings!$B$19</f>
+        <v>10</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <f aca="false">H4+D4*Materials!$G$8+E4*Materials!$G$9+F4*Materials!$G$10+G4*Materials!$G$11</f>
+        <v>162</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <f aca="false">C4*Settings!$B$21</f>
+        <v>25</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <f aca="false">C4*Settings!$B$22</f>
+        <v>75</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <f aca="false">(J4+K4)/Settings!$B$19</f>
+        <v>10</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <f aca="false">H5+D5*Materials!$G$8+E5*Materials!$G$9+F5*Materials!$G$10+G5*Materials!$G$11</f>
+        <v>470</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <f aca="false">C5*Settings!$B$21</f>
+        <v>25</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <f aca="false">C5*Settings!$B$22</f>
+        <v>75</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <f aca="false">(J5+K5)/Settings!$B$19</f>
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <f aca="false">H6+D6*Materials!$G$8+E6*Materials!$G$9+F6*Materials!$G$10+G6*Materials!$G$11</f>
+        <v>250</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <f aca="false">C6*Settings!$B$21</f>
+        <v>50</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <f aca="false">C6*Settings!$B$22</f>
+        <v>150</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <f aca="false">(J6+K6)/Settings!$B$19</f>
+        <v>20</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <f aca="false">H7+D7*Materials!$G$8+E7*Materials!$G$9+F7*Materials!$G$10+G7*Materials!$G$11</f>
+        <v>350</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <f aca="false">C7*Settings!$B$21</f>
+        <v>50</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <f aca="false">C7*Settings!$B$22</f>
+        <v>150</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <f aca="false">(J7+K7)/Settings!$B$19</f>
+        <v>20</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <f aca="false">H8+D8*Materials!$G$8+E8*Materials!$G$9+F8*Materials!$G$10+G8*Materials!$G$11</f>
+        <v>510</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <f aca="false">C8*Settings!$B$21</f>
+        <v>50</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <f aca="false">C8*Settings!$B$22</f>
+        <v>150</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <f aca="false">(J8+K8)/Settings!$B$19</f>
+        <v>20</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <f aca="false">H9+D9*Materials!$G$8+E9*Materials!$G$9+F9*Materials!$G$10+G9*Materials!$G$11</f>
+        <v>980</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <f aca="false">C9*Settings!$B$21</f>
+        <v>75</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <f aca="false">C9*Settings!$B$22</f>
+        <v>225</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <f aca="false">(J9+K9)/Settings!$B$19</f>
+        <v>30</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <f aca="false">H10+D10*Materials!$G$8+E10*Materials!$G$9+F10*Materials!$G$10+G10*Materials!$G$11</f>
+        <v>1500</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <f aca="false">C10*Settings!$B$21</f>
+        <v>100</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <f aca="false">C10*Settings!$B$22</f>
+        <v>300</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <f aca="false">(J10+K10)/Settings!$B$19</f>
+        <v>40</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <f aca="false">IF($C2&gt;1,"—",$B2/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <f aca="false">IF($C2&gt;2,"—",$B2/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <f aca="false">IF($C2&gt;3,"—",$B2/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <f aca="false">IF($C3&gt;1,"—",$B3/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <f aca="false">IF($C3&gt;2,"—",$B3/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <f aca="false">IF($C3&gt;3,"—",$B3/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <f aca="false">IF($C4&gt;1,"—",$B4/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1.25</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <f aca="false">IF($C4&gt;2,"—",$B4/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <f aca="false">IF($C4&gt;3,"—",$B4/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <f aca="false">IF($C5&gt;1,"—",$B5/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.25</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <f aca="false">IF($C5&gt;2,"—",$B5/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <f aca="false">IF($C5&gt;3,"—",$B5/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.28125</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">IF($C6&gt;1,"—",$B6/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <f aca="false">IF($C6&gt;2,"—",$B6/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <f aca="false">IF($C6&gt;3,"—",$B6/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.09375</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">IF($C7&gt;1,"—",$B7/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <f aca="false">IF($C7&gt;2,"—",$B7/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <f aca="false">IF($C7&gt;3,"—",$B7/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.03125</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <f aca="false">IF($C8&gt;1,"—",$B8/(Settings!$B$2*Parts!$F$5))</f>
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <f aca="false">IF($C8&gt;2,"—",$B8/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <f aca="false">IF($C8&gt;3,"—",$B8/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.09375</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <f aca="false">IF($C9&gt;1,"—",$B9/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1.25</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <f aca="false">IF($C9&gt;2,"—",$B9/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <f aca="false">IF($C9&gt;3,"—",$B9/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <f aca="false">IF($C10&gt;1,"—",$B10/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <f aca="false">IF($C10&gt;2,"—",$B10/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <f aca="false">IF($C10&gt;3,"—",$B10/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <f aca="false">IF($C11&gt;1,"—",$B11/(Settings!$B$2*Parts!$F$5))</f>
+        <v>2.75</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <f aca="false">IF($C11&gt;2,"—",$B11/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <f aca="false">IF($C11&gt;3,"—",$B11/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <f aca="false">IF($C12&gt;1,"—",$B12/(Settings!$B$2*Parts!$F$5))</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <f aca="false">IF($C12&gt;2,"—",$B12/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <f aca="false">IF($C12&gt;3,"—",$B12/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="str">
+        <f aca="false">IF($C13&gt;1,"—",$B13/(Settings!$B$2*Parts!$F$5))</f>
+        <v>—</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <f aca="false">IF($C13&gt;2,"—",$B13/(Settings!$B$2*Parts!$F$6))</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <f aca="false">IF($C13&gt;3,"—",$B13/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="18" t="str">
+        <f aca="false">IF($C14&gt;1,"—",$B14/(Settings!$B$2*Parts!$F$5))</f>
+        <v>—</v>
+      </c>
+      <c r="E14" s="18" t="str">
+        <f aca="false">IF($C14&gt;2,"—",$B14/(Settings!$B$2*Parts!$F$6))</f>
+        <v>—</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <f aca="false">IF($C14&gt;3,"—",$B14/(Settings!$B$2*Parts!$F$7))</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <f aca="false">IF($C15&gt;1,"—",$B15/(Settings!$B$2*Parts!$F$5))</f>
+        <v>10</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <f aca="false">IF($C15&gt;2,"—",$B15/(Settings!$B$2*Parts!$F$6))</f>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <f aca="false">IF($C15&gt;3,"—",$B15/(Settings!$B$2*Parts!$F$7))</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2725,40 +4022,40 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>152</v>
+      <c r="A1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="D2" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
         <v>1</v>
       </c>
@@ -2777,16 +4074,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="16" t="n">
+        <v>129</v>
+      </c>
+      <c r="D3" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
         <v>0.8</v>
       </c>
@@ -2805,16 +4102,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
         <v>0.55</v>
       </c>
@@ -2833,16 +4130,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="D5" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
         <v>1</v>
       </c>
@@ -2861,16 +4158,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="16" t="n">
+        <v>129</v>
+      </c>
+      <c r="D6" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
         <v>0.8</v>
       </c>
@@ -2889,16 +4186,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="D7" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
         <v>0.55</v>
       </c>
@@ -2917,16 +4214,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="16" t="n">
+        <v>126</v>
+      </c>
+      <c r="D8" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
         <v>1</v>
       </c>
@@ -2945,16 +4242,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="16" t="n">
+        <v>129</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
         <v>0.8</v>
       </c>
@@ -2973,16 +4270,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
         <v>0.55</v>
       </c>
@@ -3000,621 +4297,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f aca="false">Parts!D6</f>
-        <v>60</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <f aca="false">SUM($C$2:C2)-SUM($B$2:B2)</f>
-        <v>-60</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="12" t="n">
-        <f aca="false">Caves!O2</f>
-        <v>80</v>
-      </c>
-      <c r="D3" s="18" t="n">
-        <f aca="false">SUM($C$2:C3)-SUM($B$2:B3)</f>
-        <v>-140</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <f aca="false">Caves!N2</f>
-        <v>300</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <f aca="false">SUM($C$2:C4)-SUM($B$2:B4)</f>
-        <v>160</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="12" t="n">
-        <f aca="false">Parts!D3</f>
-        <v>120</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <f aca="false">SUM($C$2:C5)-SUM($B$2:B5)</f>
-        <v>40</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="12" t="n">
-        <f aca="false">Parts!D9</f>
-        <v>150</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <f aca="false">SUM($C$2:C6)-SUM($B$2:B6)</f>
-        <v>-110</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <f aca="false">Caves!O3</f>
-        <v>200</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <f aca="false">SUM($C$2:C7)-SUM($B$2:B7)</f>
-        <v>-310</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <f aca="false">Caves!N3</f>
-        <v>800</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <f aca="false">SUM($C$2:C8)-SUM($B$2:B8)</f>
-        <v>490</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="12" t="n">
-        <f aca="false">Parts!D7</f>
-        <v>900</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <f aca="false">SUM($C$2:C9)-SUM($B$2:B9)</f>
-        <v>-410</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="12" t="n">
-        <f aca="false">Caves!O4</f>
-        <v>500</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <f aca="false">SUM($C$2:C10)-SUM($B$2:B10)</f>
-        <v>-910</v>
-      </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <f aca="false">Caves!N4</f>
-        <v>2000</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <f aca="false">SUM($C$2:C11)-SUM($B$2:B11)</f>
-        <v>1090</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A12-1))</f>
-        <v>1.4</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A12-1))</f>
-        <v>2</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <f aca="false">C12*(1+$B$5*($B$6-1))/B12*60</f>
-        <v>126.857142857143</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <f aca="false">$B$7*A12</f>
-        <v>0.08</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A13-1))</f>
-        <v>1.07692307692308</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A13-1))</f>
-        <v>3</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <f aca="false">C13*(1+$B$5*($B$6-1))/B13*60</f>
-        <v>247.371428571429</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <f aca="false">$B$7*A13</f>
-        <v>0.16</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A13-2),0)</f>
-        <v>120</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <f aca="false">G12+F13</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A14-1))</f>
-        <v>0.875</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A14-1))</f>
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <f aca="false">C14*(1+$B$5*($B$6-1))/B14*60</f>
-        <v>405.942857142857</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <f aca="false">$B$7*A14</f>
-        <v>0.24</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A14-2),0)</f>
-        <v>216</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <f aca="false">G13+F14</f>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A15-1))</f>
-        <v>0.736842105263158</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A15-1))</f>
-        <v>5</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <f aca="false">C15*(1+$B$5*($B$6-1))/B15*60</f>
-        <v>602.571428571429</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <f aca="false">$B$7*A15</f>
-        <v>0.32</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A15-2),0)</f>
-        <v>389</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <f aca="false">G14+F15</f>
-        <v>725</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A16-1))</f>
-        <v>0.636363636363636</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A16-1))</f>
-        <v>6</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <f aca="false">C16*(1+$B$5*($B$6-1))/B16*60</f>
-        <v>837.257142857143</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <f aca="false">$B$7*A16</f>
-        <v>0.4</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A16-2),0)</f>
-        <v>700</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <f aca="false">G15+F16</f>
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A17-1))</f>
-        <v>0.56</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A17-1))</f>
-        <v>7</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <f aca="false">C17*(1+$B$5*($B$6-1))/B17*60</f>
-        <v>1110</v>
-      </c>
-      <c r="E17" s="21" t="n">
-        <f aca="false">$B$7*A17</f>
-        <v>0.48</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A17-2),0)</f>
-        <v>1260</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <f aca="false">G16+F17</f>
-        <v>2685</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B18" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A18-1))</f>
-        <v>0.5</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A18-1))</f>
-        <v>8</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <f aca="false">C18*(1+$B$5*($B$6-1))/B18*60</f>
-        <v>1420.8</v>
-      </c>
-      <c r="E18" s="21" t="n">
-        <f aca="false">$B$7*A18</f>
-        <v>0.56</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A18-2),0)</f>
-        <v>2267</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <f aca="false">G17+F18</f>
-        <v>4952</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A19-1))</f>
-        <v>0.451612903225806</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A19-1))</f>
-        <v>9</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <f aca="false">C19*(1+$B$5*($B$6-1))/B19*60</f>
-        <v>1769.65714285714</v>
-      </c>
-      <c r="E19" s="21" t="n">
-        <f aca="false">$B$7*A19</f>
-        <v>0.64</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A19-2),0)</f>
-        <v>4081</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <f aca="false">G18+F19</f>
-        <v>9033</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A20-1))</f>
-        <v>0.411764705882353</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A20-1))</f>
-        <v>10</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <f aca="false">C20*(1+$B$5*($B$6-1))/B20*60</f>
-        <v>2156.57142857143</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <f aca="false">$B$7*A20</f>
-        <v>0.72</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A20-2),0)</f>
-        <v>7347</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <f aca="false">G19+F20</f>
-        <v>16380</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="19" t="n">
-        <f aca="false">$B$2/(1+$B$3*(A21-1))</f>
-        <v>0.378378378378378</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <f aca="false">$B$4*(1+0.5*(A21-1))</f>
-        <v>11</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <f aca="false">C21*(1+$B$5*($B$6-1))/B21*60</f>
-        <v>2581.54285714286</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <f aca="false">$B$7*A21</f>
-        <v>0.8</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <f aca="false">ROUND($B$8*$B$9^(A21-2),0)</f>
-        <v>13224</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <f aca="false">G20+F21</f>
-        <v>29604</v>
+      <c r="A12" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="234">
   <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.8)</t>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.8.1)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -2857,7 +2857,7 @@
         <v>155</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2865,7 +2865,7 @@
         <v>156</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,7 +2873,7 @@
         <v>157</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2881,7 +2881,7 @@
         <v>158</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2933,15 +2933,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H8" s="13" t="n">
         <f aca="false">B8*$B$2+C8*$B$3+D8*$B$4+E8*$B$5</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">G8-H8</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2964,15 +2964,15 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H9" s="13" t="n">
         <f aca="false">B9*$B$2+C9*$B$3+D9*$B$4+E9*$B$5</f>
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I9" s="16" t="n">
         <f aca="false">G9-H9</f>
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2995,15 +2995,15 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">B10*$B$2+C10*$B$3+D10*$B$4+E10*$B$5</f>
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="I10" s="16" t="n">
         <f aca="false">G10-H10</f>
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,15 +3026,15 @@
         <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">B11*$B$2+C11*$B$3+D11*$B$4+E11*$B$5</f>
-        <v>265</v>
+        <v>398</v>
       </c>
       <c r="I11" s="16" t="n">
         <f aca="false">G11-H11</f>
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I2" s="13" t="n">
         <f aca="false">H2+D2*Materials!$G$8+E2*Materials!$G$9+F2*Materials!$G$10+G2*Materials!$G$11</f>
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="J2" s="12" t="n">
         <f aca="false">C2*Settings!$B$21</f>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="I3" s="13" t="n">
         <f aca="false">H3+D3*Materials!$G$8+E3*Materials!$G$9+F3*Materials!$G$10+G3*Materials!$G$11</f>
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="J3" s="12" t="n">
         <f aca="false">C3*Settings!$B$21</f>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I4" s="13" t="n">
         <f aca="false">H4+D4*Materials!$G$8+E4*Materials!$G$9+F4*Materials!$G$10+G4*Materials!$G$11</f>
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="J4" s="12" t="n">
         <f aca="false">C4*Settings!$B$21</f>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">H5+D5*Materials!$G$8+E5*Materials!$G$9+F5*Materials!$G$10+G5*Materials!$G$11</f>
-        <v>470</v>
+        <v>630</v>
       </c>
       <c r="J5" s="12" t="n">
         <f aca="false">C5*Settings!$B$21</f>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">H6+D6*Materials!$G$8+E6*Materials!$G$9+F6*Materials!$G$10+G6*Materials!$G$11</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="J6" s="12" t="n">
         <f aca="false">C6*Settings!$B$21</f>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">H7+D7*Materials!$G$8+E7*Materials!$G$9+F7*Materials!$G$10+G7*Materials!$G$11</f>
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">C7*Settings!$B$21</f>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="I8" s="13" t="n">
         <f aca="false">H8+D8*Materials!$G$8+E8*Materials!$G$9+F8*Materials!$G$10+G8*Materials!$G$11</f>
-        <v>510</v>
+        <v>640</v>
       </c>
       <c r="J8" s="12" t="n">
         <f aca="false">C8*Settings!$B$21</f>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I9" s="13" t="n">
         <f aca="false">H9+D9*Materials!$G$8+E9*Materials!$G$9+F9*Materials!$G$10+G9*Materials!$G$11</f>
-        <v>980</v>
+        <v>1270</v>
       </c>
       <c r="J9" s="12" t="n">
         <f aca="false">C9*Settings!$B$21</f>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I10" s="13" t="n">
         <f aca="false">H10+D10*Materials!$G$8+E10*Materials!$G$9+F10*Materials!$G$10+G10*Materials!$G$11</f>
-        <v>1500</v>
+        <v>1950</v>
       </c>
       <c r="J10" s="12" t="n">
         <f aca="false">C10*Settings!$B$21</f>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -18,6 +18,8 @@
     <sheet name="Dig times" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Battery" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Progress" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Tools &amp; skills" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Hazards" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="234">
-  <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.8.1)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="286">
+  <si>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.9)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -73,6 +75,12 @@
     <t xml:space="preserve">Mods – every computer mod: shape, build cost, Flux to upgrade and how long the nano-bot takes to make it</t>
   </si>
   <si>
+    <t xml:space="preserve">Tools &amp; skills – tool prices and belt slots; active skills, their recharge times and battery cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazards – how much sand, boulders, water and gas take when they hit you</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dig times – seconds to break each block with each arm tier ("—" = too hard for that tier)</t>
   </si>
   <si>
@@ -731,6 +739,156 @@
   </si>
   <si>
     <t xml:space="preserve">Relic rewards only. A negative running total is what you need to earn from block coins, caches and selling ore before that step (see Block coins). Mods are extra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price (coins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max per slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full slot costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it does</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blast charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaks a 3×3 area, even hard rock (you collect what breaks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support beam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stops sand and boulders; keeps unstable rock within 1 block still</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lights a 7-block radius for 30 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grapple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swings across up to 3 blocks of chasm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belt slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base belt slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each tool type takes one slot. Pip buys tools back at full price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery per use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recharge Lv 1 (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv 2 (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lv 3 (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses per minute at Lv 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drill Burst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scan Pulse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skills go in the computer's bottom row (opens with the Core Heart), one at a time. The nano-bot recharges them; upgrades use Flux like other mods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery lost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore lost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave-in (unstable rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 s shake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets off unstable rock within 2.2 blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sand slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 s per block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slides toward the entrance into open space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling boulder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 s rumble, then 0.14 s per block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push one by walking into it for 0.3 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas explosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 s fuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hits within 1.8 blocks; clears a 3×3 area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flood water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 per second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 s per block, 10 blocks a pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wading runs at 55% speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Shield blocks the whole hit. Every cave slopes toward its entrance, so sand and boulders move that way.</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1307,8 +1465,18 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="2" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1338,24 +1506,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">Parts!D6</f>
@@ -1366,12 +1534,12 @@
         <v>-60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">Caves!O2</f>
@@ -1382,12 +1550,12 @@
         <v>-140</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C4" s="12" t="n">
         <f aca="false">Caves!N2</f>
@@ -1398,12 +1566,12 @@
         <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">Parts!D3</f>
@@ -1414,12 +1582,12 @@
         <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Parts!D9</f>
@@ -1430,12 +1598,12 @@
         <v>-110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">Caves!O3</f>
@@ -1449,7 +1617,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">Caves!N3</f>
@@ -1460,12 +1628,12 @@
         <v>490</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">Parts!D7</f>
@@ -1476,12 +1644,12 @@
         <v>-410</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">Caves!O4</f>
@@ -1495,7 +1663,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">Caves!N4</f>
@@ -1506,12 +1674,546 @@
         <v>1090</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <f aca="false">C2*D2</f>
+        <v>120</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <f aca="false">C3*D3</f>
+        <v>75</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <f aca="false">C4*D4</f>
+        <v>50</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <f aca="false">C5*D5</f>
+        <v>120</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <f aca="false">$B$12+0</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <f aca="false">$B$12+1</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <f aca="false">$B$12+2</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <f aca="false">60/K16</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <f aca="false">60/K17</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <f aca="false">60/K18</f>
+        <v>6.66666666666667</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <f aca="false">60/K19</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -1540,244 +2242,244 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>80</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>60</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>160</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>75</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1816,61 +2518,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1878,19 +2580,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>0.025</v>
@@ -1911,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N2" s="11" t="n">
         <v>300</v>
@@ -1932,7 +2634,7 @@
         <v>160</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1940,19 +2642,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>0.03</v>
@@ -1973,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N3" s="11" t="n">
         <v>800</v>
@@ -1994,7 +2696,7 @@
         <v>240</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2002,19 +2704,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>0.025</v>
@@ -2035,7 +2737,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N4" s="11" t="n">
         <v>2000</v>
@@ -2056,17 +2758,17 @@
         <v>320</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2101,54 +2803,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -2160,25 +2862,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>3</v>
@@ -2190,25 +2892,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -2220,28 +2922,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">SUM(D5:D5)</f>
@@ -2250,28 +2952,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">SUM(D5:D6)</f>
@@ -2280,28 +2982,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>900</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -2310,25 +3012,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -2340,25 +3042,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>16</v>
@@ -2370,25 +3072,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>240</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>30</v>
@@ -2400,25 +3102,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
@@ -2430,25 +3132,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.8</v>
@@ -2460,25 +3162,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.55</v>
@@ -2490,7 +3192,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">SUM(D2:D13)</f>
@@ -2525,27 +3227,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -2568,7 +3270,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
@@ -2591,7 +3293,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
@@ -2614,7 +3316,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -2637,7 +3339,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>4</v>
@@ -2660,7 +3362,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -2683,7 +3385,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -2706,7 +3408,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -2729,29 +3431,29 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">C2</f>
@@ -2772,7 +3474,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B14" s="5" t="n">
         <f aca="false">D4</f>
@@ -2793,7 +3495,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">E5</f>
@@ -2814,7 +3516,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2846,15 +3548,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -2862,7 +3564,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>24</v>
@@ -2870,7 +3572,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>68</v>
@@ -2878,7 +3580,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>165</v>
@@ -2886,36 +3588,36 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -2946,7 +3648,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -2977,7 +3679,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
@@ -3008,7 +3710,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>0</v>
@@ -3039,7 +3741,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3076,60 +3778,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="H1" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -3175,15 +3877,15 @@
         <v>0.2</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -3229,15 +3931,15 @@
         <v>0.3</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
@@ -3283,15 +3985,15 @@
         <v>0.3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -3337,15 +4039,15 @@
         <v>2</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
@@ -3391,15 +4093,15 @@
         <v>0.6</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
@@ -3445,15 +4147,15 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>2</v>
@@ -3499,15 +4201,15 @@
         <v>0.4</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -3553,15 +4255,15 @@
         <v>5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4</v>
@@ -3607,17 +4309,17 @@
         <v>0.45</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3648,27 +4350,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2</v>
@@ -3691,7 +4393,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>4</v>
@@ -3714,7 +4416,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>5</v>
@@ -3737,7 +4439,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>9</v>
@@ -3760,7 +4462,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
@@ -3783,7 +4485,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1</v>
@@ -3806,7 +4508,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>3</v>
@@ -3829,7 +4531,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>5</v>
@@ -3852,7 +4554,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>8</v>
@@ -3875,7 +4577,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>11</v>
@@ -3898,7 +4600,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -3921,7 +4623,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>10</v>
@@ -3944,7 +4646,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>16</v>
@@ -3967,7 +4669,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>40</v>
@@ -3990,7 +4692,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -4023,37 +4725,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D2" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4074,14 +4776,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D3" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4102,14 +4804,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -4130,14 +4832,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4158,14 +4860,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4186,14 +4888,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -4214,14 +4916,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4242,14 +4944,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4270,14 +4972,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -4298,7 +5000,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Progress" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Tools &amp; skills" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Hazards" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Weapons" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Enemies" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,9 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="286">
-  <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.9)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="344">
+  <si>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.11)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -81,6 +83,12 @@
     <t xml:space="preserve">Hazards – how much sand, boulders, water and gas take when they hit you</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapons – every weapon arm, its damage per second at Mk I–III, and how well it mines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemies – enemy and boss stats, and how many seconds each weapon takes to beat them</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dig times – seconds to break each block with each arm tier ("—" = too hard for that tier)</t>
   </si>
   <si>
@@ -889,6 +897,174 @@
   </si>
   <si>
     <t xml:space="preserve">A Shield blocks the whole hit. Every cave slopes toward its entrance, so sand and boulders move that way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage (Mk I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooldown (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS Mk II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS Mk III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block hit share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block damage / s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breaks up to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free starter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rock Hammer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cracks armour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivet Gun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravity Bulwark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull + 0.9 s stun, halves frontal damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stun Pulse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 s stun, marks for 4 s (+50% damage, no armour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mk multipliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dig arms for comparison: Rock Claws 4, Drill Arms 12, Plasma Cutters 32 block damage a second (plus the cone: 40% to the sides, 30% behind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enemy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage to hull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrench Mk I (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammer Mk I (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivet Mk I (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollowmouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave Bat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spitter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollowmouth (caves 2–3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rock Crab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rustvale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magma Mite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rustvale (groups of 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grub Mother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 1 mini-boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystal Warden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 2 mini-boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basalt Golem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 3 boss (drops the Core Heart)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seconds of non-stop hitting. Armour is ignored by the Rock Hammer and by marked or stunned enemies. Hull: 60 / 100 / 160 by Tank tier; it repairs at outposts.</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1206,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1112,6 +1288,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1367,7 +1547,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1475,8 +1655,18 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="2" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1506,24 +1696,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">Parts!D6</f>
@@ -1534,12 +1724,12 @@
         <v>-60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">Caves!O2</f>
@@ -1550,12 +1740,12 @@
         <v>-140</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C4" s="12" t="n">
         <f aca="false">Caves!N2</f>
@@ -1566,12 +1756,12 @@
         <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">Parts!D3</f>
@@ -1582,12 +1772,12 @@
         <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Parts!D9</f>
@@ -1598,12 +1788,12 @@
         <v>-110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">Caves!O3</f>
@@ -1617,7 +1807,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">Caves!N3</f>
@@ -1628,12 +1818,12 @@
         <v>490</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">Parts!D7</f>
@@ -1644,12 +1834,12 @@
         <v>-410</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">Caves!O4</f>
@@ -1663,7 +1853,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">Caves!N4</f>
@@ -1674,12 +1864,12 @@
         <v>1090</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1715,27 +1905,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1751,12 +1941,12 @@
         <v>120</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1772,12 +1962,12 @@
         <v>75</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -1793,12 +1983,12 @@
         <v>50</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -1814,20 +2004,20 @@
         <v>120</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">$B$12+0</f>
@@ -1836,7 +2026,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">$B$12+1</f>
@@ -1845,7 +2035,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">$B$12+2</f>
@@ -1854,7 +2044,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>3</v>
@@ -1862,50 +2052,50 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
@@ -1944,7 +2134,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1</v>
@@ -1983,7 +2173,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
@@ -2022,7 +2212,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2</v>
@@ -2061,7 +2251,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2093,27 +2283,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
@@ -2125,15 +2315,15 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -2145,15 +2335,15 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
@@ -2165,15 +2355,15 @@
         <v>0.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>3</v>
@@ -2185,35 +2375,697 @@
         <v>0.3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <f aca="false">D2*$C$9/(E2*$C$10)</f>
+        <v>6.66666666666667</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <f aca="false">D2*$D$9/(E2*$D$10)</f>
+        <v>11.1111111111111</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <f aca="false">D2*$E$9/(E2*$E$10)</f>
+        <v>18.3333333333333</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <f aca="false">F2*I2</f>
+        <v>3.33333333333333</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <f aca="false">D3*$C$9/(E3*$C$10)</f>
+        <v>11.4285714285714</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <f aca="false">D3*$D$9/(E3*$D$10)</f>
+        <v>19.047619047619</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <f aca="false">D3*$E$9/(E3*$E$10)</f>
+        <v>31.4285714285714</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <f aca="false">F3*I3</f>
+        <v>10.2857142857143</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <f aca="false">D4*$C$9/(E4*$C$10)</f>
+        <v>10</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <f aca="false">D4*$D$9/(E4*$D$10)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <f aca="false">D4*$E$9/(E4*$E$10)</f>
+        <v>27.5</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <f aca="false">F4*I4</f>
+        <v>2.5</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>260</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <f aca="false">D5*$C$9/(E5*$C$10)</f>
+        <v>1.25</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <f aca="false">D5*$D$9/(E5*$D$10)</f>
+        <v>2.08333333333333</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <f aca="false">D5*$E$9/(E5*$E$10)</f>
+        <v>3.4375</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <f aca="false">F5*I5</f>
+        <v>0.25</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">D6*$C$9/(E6*$C$10)</f>
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <f aca="false">D6*$D$9/(E6*$D$10)</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <f aca="false">D6*$E$9/(E6*$E$10)</f>
+        <v>1.1</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <f aca="false">F6*I6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <f aca="false">C2/(Weapons!$F$2*(1-F2))</f>
+        <v>1.5</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <f aca="false">C2/Weapons!$F$3</f>
+        <v>0.875</v>
+      </c>
+      <c r="J2" s="21" t="n">
+        <f aca="false">C2/(Weapons!$F$4*(1-F2))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <f aca="false">C3/(Weapons!$F$2*(1-F3))</f>
+        <v>0.75</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <f aca="false">C3/Weapons!$F$3</f>
+        <v>0.4375</v>
+      </c>
+      <c r="J3" s="21" t="n">
+        <f aca="false">C3/(Weapons!$F$4*(1-F3))</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <f aca="false">C4/(Weapons!$F$2*(1-F4))</f>
+        <v>2.1</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <f aca="false">C4/Weapons!$F$3</f>
+        <v>1.225</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <f aca="false">C4/(Weapons!$F$4*(1-F4))</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <f aca="false">C5/(Weapons!$F$2*(1-F5))</f>
+        <v>11</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <f aca="false">C5/Weapons!$F$3</f>
+        <v>1.925</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <f aca="false">C5/(Weapons!$F$4*(1-F5))</f>
+        <v>7.33333333333333</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <f aca="false">C6/(Weapons!$F$2*(1-F6))</f>
+        <v>0.45</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <f aca="false">C6/Weapons!$F$3</f>
+        <v>0.2625</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <f aca="false">C6/(Weapons!$F$4*(1-F6))</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <f aca="false">C7/(Weapons!$F$2*(1-F7))</f>
+        <v>10.5</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <f aca="false">C7/Weapons!$F$3</f>
+        <v>6.125</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <f aca="false">C7/(Weapons!$F$4*(1-F7))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <f aca="false">C8/(Weapons!$F$2*(1-F8))</f>
+        <v>48</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <f aca="false">C8/Weapons!$F$3</f>
+        <v>14</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <f aca="false">C8/(Weapons!$F$4*(1-F8))</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <f aca="false">C9/(Weapons!$F$2*(1-F9))</f>
+        <v>67.5</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <f aca="false">C9/Weapons!$F$3</f>
+        <v>39.375</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <f aca="false">C9/(Weapons!$F$4*(1-F9))</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -2242,244 +3094,244 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>80</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>60</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>160</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>75</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2518,61 +3370,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2580,19 +3432,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>0.025</v>
@@ -2613,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N2" s="11" t="n">
         <v>300</v>
@@ -2634,7 +3486,7 @@
         <v>160</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2642,19 +3494,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>0.03</v>
@@ -2675,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N3" s="11" t="n">
         <v>800</v>
@@ -2696,7 +3548,7 @@
         <v>240</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2704,19 +3556,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>0.025</v>
@@ -2737,7 +3589,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N4" s="11" t="n">
         <v>2000</v>
@@ -2758,17 +3610,17 @@
         <v>320</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2803,54 +3655,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -2862,25 +3714,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>3</v>
@@ -2892,25 +3744,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -2922,28 +3774,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">SUM(D5:D5)</f>
@@ -2952,28 +3804,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">SUM(D5:D6)</f>
@@ -2982,28 +3834,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>900</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -3012,25 +3864,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -3042,25 +3894,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>16</v>
@@ -3072,25 +3924,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>240</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>30</v>
@@ -3102,25 +3954,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
@@ -3132,25 +3984,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.8</v>
@@ -3162,25 +4014,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.55</v>
@@ -3192,7 +4044,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">SUM(D2:D13)</f>
@@ -3227,27 +4079,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -3270,7 +4122,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
@@ -3293,7 +4145,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
@@ -3316,7 +4168,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -3339,7 +4191,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>4</v>
@@ -3362,7 +4214,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -3385,7 +4237,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -3408,7 +4260,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -3431,29 +4283,29 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">C2</f>
@@ -3474,7 +4326,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B14" s="5" t="n">
         <f aca="false">D4</f>
@@ -3495,7 +4347,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">E5</f>
@@ -3516,7 +4368,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3548,15 +4400,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -3564,7 +4416,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>24</v>
@@ -3572,7 +4424,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>68</v>
@@ -3580,7 +4432,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>165</v>
@@ -3588,36 +4440,36 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>156</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -3648,7 +4500,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -3679,7 +4531,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
@@ -3710,7 +4562,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>0</v>
@@ -3741,7 +4593,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3778,60 +4630,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>168</v>
-      </c>
       <c r="H1" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -3877,15 +4729,15 @@
         <v>0.2</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -3931,15 +4783,15 @@
         <v>0.3</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
@@ -3985,15 +4837,15 @@
         <v>0.3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -4039,15 +4891,15 @@
         <v>2</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
@@ -4093,15 +4945,15 @@
         <v>0.6</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
@@ -4147,15 +4999,15 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>2</v>
@@ -4201,15 +5053,15 @@
         <v>0.4</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -4255,15 +5107,15 @@
         <v>5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4</v>
@@ -4309,17 +5161,17 @@
         <v>0.45</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4350,27 +5202,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2</v>
@@ -4393,7 +5245,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>4</v>
@@ -4416,7 +5268,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>5</v>
@@ -4439,7 +5291,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>9</v>
@@ -4462,7 +5314,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
@@ -4485,7 +5337,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1</v>
@@ -4508,7 +5360,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>3</v>
@@ -4531,7 +5383,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>5</v>
@@ -4554,7 +5406,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>8</v>
@@ -4577,7 +5429,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>11</v>
@@ -4600,7 +5452,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -4623,7 +5475,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>10</v>
@@ -4646,7 +5498,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>16</v>
@@ -4669,7 +5521,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>40</v>
@@ -4692,7 +5544,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4725,37 +5577,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D2" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4776,14 +5628,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D3" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4804,14 +5656,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -4832,14 +5684,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4860,14 +5712,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4888,14 +5740,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -4916,14 +5768,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -4944,14 +5796,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -4972,14 +5824,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -5000,7 +5852,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Hazards" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Weapons" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Enemies" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Flux upgrades" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="366">
   <si>
     <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.11)</t>
   </si>
@@ -1065,6 +1066,72 @@
   </si>
   <si>
     <t xml:space="preserve">Seconds of non-stop hitting. Armour is ignored by the Rock Hammer and by marked or stunned enemies. Hull: 60 / 100 / 160 by Tank tier; it repairs at outposts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total at max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnet (blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickup range; pull speed +25% a level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hull plating (hull)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base = Small Tank hull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraction of each hit removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field repair (hull/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only in the caves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplies every weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Flux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours of 1 bot (10/min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxing all five upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ore drops: each ore block holds 1–4 pieces (average 2.5). Pieces stay on the floor until you leave the cave.</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1273,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1292,6 +1359,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3079,6 +3150,293 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <f aca="false">B2*C2</f>
+        <v>3.5</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <f aca="false">E2+D2</f>
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">B3*C3</f>
+        <v>75</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <f aca="false">E3+D3</f>
+        <v>135</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <f aca="false">B4*C4</f>
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <f aca="false">E4+D4</f>
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">B5*C5</f>
+        <v>2.5</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <f aca="false">E5+D5</f>
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <f aca="false">B6*C6</f>
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <f aca="false">E6+D6</f>
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <f aca="false">SUM($B$10:B10)</f>
+        <v>30</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <f aca="false">C10/600</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <f aca="false">SUM($B$10:B11)</f>
+        <v>90</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <f aca="false">C11/600</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">SUM($B$10:B12)</f>
+        <v>210</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <f aca="false">C12/600</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <f aca="false">SUM($B$10:B13)</f>
+        <v>450</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <f aca="false">C13/600</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <f aca="false">SUM($B$10:B14)</f>
+        <v>850</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <f aca="false">C14/600</f>
+        <v>1.41666666666667</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <f aca="false">C14*5</f>
+        <v>4250</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <f aca="false">C16/600</f>
+        <v>7.08333333333333</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="369">
   <si>
     <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.11)</t>
   </si>
@@ -1116,6 +1116,15 @@
     <t xml:space="preserve">Multiplies every weapon</t>
   </si>
   <si>
+    <t xml:space="preserve">Prospector's luck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chance of +1 ore piece per ore block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added to the canopy scanner (Glass Bubble has 0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Level</t>
   </si>
   <si>
@@ -1128,7 +1137,7 @@
     <t xml:space="preserve">Hours of 1 bot (10/min)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maxing all five upgrades</t>
+    <t xml:space="preserve">Maxing all seven upgrades</t>
   </si>
   <si>
     <t xml:space="preserve">Ore drops: each ore block holds 1–4 pieces (average 2.5). Pieces stay on the floor until you leave the cave.</t>
@@ -3314,18 +3323,68 @@
         <v>359</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <f aca="false">B7*C7</f>
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <f aca="false">E7+D7</f>
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <f aca="false">B8*C8</f>
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <f aca="false">E8+D8</f>
+        <v>5</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3410,20 +3469,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C16" s="13" t="n">
-        <f aca="false">C14*5</f>
-        <v>4250</v>
+        <f aca="false">C14*7</f>
+        <v>5950</v>
       </c>
       <c r="D16" s="15" t="n">
         <f aca="false">C16/600</f>
-        <v>7.08333333333333</v>
+        <v>9.91666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -23,6 +23,7 @@
     <sheet name="Weapons" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Enemies" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="Flux upgrades" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Contracts" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="406">
   <si>
     <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.11)</t>
   </si>
@@ -333,6 +334,30 @@
     <t xml:space="preserve">Plasma Cutters (obsidian seal)</t>
   </si>
   <si>
+    <t xml:space="preserve">Scrap Tunnels (Rustvale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brass Governor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slag Works (Rustvale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slag Crown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Crucible (Rustvale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foundry Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beat the Foundry Titan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rustvale extras: Cave 4 has scrap blocks (3.5%, 9 coins × multiplier) and 10 steam vents; Cave 5 has scrap (2%), 5 vents and 10 hidden lava pockets; Cave 6 has 4 vents, 8 lava pockets and two lava rivers (its chasms).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hard rock is rarer near the cave mouth: its chance scales from 40% of the listed value at the entrance to 140% at the relic.</t>
   </si>
   <si>
@@ -1065,6 +1090,24 @@
     <t xml:space="preserve">Cave 3 boss (drops the Core Heart)</t>
   </si>
   <si>
+    <t xml:space="preserve">Scrap Hauler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 4 mini-boss (charges, crashes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slag Golem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 5 mini-boss (slam, mites)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foundry Titan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cave 6 boss (slag volleys, slam; drops the Foundry Heart)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seconds of non-stop hitting. Armour is ignored by the Rock Hammer and by marked or stunned enemies. Hull: 60 / 100 / 160 by Tank tier; it repairs at outposts.</t>
   </si>
   <si>
@@ -1141,6 +1184,75 @@
   </si>
   <si>
     <t xml:space="preserve">Ore drops: each ore block holds 1–4 pieces (average 2.5). Pieces stay on the floor until you leave the cave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size · tier 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins (tier 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dig blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collect one kind of ore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defeat enemies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defeat one kind of enemy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send ore home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refine materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earn coins selling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open caches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reach a depth (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily bonus (all three)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin growth per tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three contracts are picked at random each day (same three all day, new ones at midnight). Tier: 0 = start, 1 = Ember Idol home, 2 = Storm Lens home, 3 = Core Heart home (Rustvale).</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1394,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1372,6 +1484,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1776,24 +1892,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">Parts!D6</f>
@@ -1804,12 +1920,12 @@
         <v>-60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">Caves!O2</f>
@@ -1820,12 +1936,12 @@
         <v>-140</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C4" s="12" t="n">
         <f aca="false">Caves!N2</f>
@@ -1836,12 +1952,12 @@
         <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">Parts!D3</f>
@@ -1852,12 +1968,12 @@
         <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Parts!D9</f>
@@ -1868,12 +1984,12 @@
         <v>-110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">Caves!O3</f>
@@ -1887,7 +2003,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">Caves!N3</f>
@@ -1898,12 +2014,12 @@
         <v>490</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">Parts!D7</f>
@@ -1914,12 +2030,12 @@
         <v>-410</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">Caves!O4</f>
@@ -1933,7 +2049,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">Caves!N4</f>
@@ -1944,12 +2060,12 @@
         <v>1090</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -1985,27 +2101,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -2021,12 +2137,12 @@
         <v>120</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -2042,12 +2158,12 @@
         <v>75</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -2063,12 +2179,12 @@
         <v>50</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -2084,20 +2200,20 @@
         <v>120</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">$B$12+0</f>
@@ -2106,7 +2222,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">$B$12+1</f>
@@ -2115,7 +2231,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">$B$12+2</f>
@@ -2124,7 +2240,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>3</v>
@@ -2132,50 +2248,50 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
@@ -2214,7 +2330,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1</v>
@@ -2253,7 +2369,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
@@ -2292,7 +2408,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2</v>
@@ -2331,7 +2447,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2363,27 +2479,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
@@ -2395,15 +2511,15 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -2415,15 +2531,15 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
@@ -2435,15 +2551,15 @@
         <v>0.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>3</v>
@@ -2455,35 +2571,35 @@
         <v>0.3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -2519,48 +2635,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>0</v>
@@ -2591,18 +2707,18 @@
         <v>3.33333333333333</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>180</v>
@@ -2633,18 +2749,18 @@
         <v>10.2857142857143</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>220</v>
@@ -2675,18 +2791,18 @@
         <v>2.5</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>260</v>
@@ -2717,18 +2833,18 @@
         <v>0.25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>300</v>
@@ -2759,18 +2875,18 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -2784,7 +2900,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
@@ -2798,7 +2914,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -2817,11 +2933,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
@@ -2833,42 +2949,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>10</v>
@@ -2900,10 +3016,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>5</v>
@@ -2935,10 +3051,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>14</v>
@@ -2970,10 +3086,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>22</v>
@@ -3005,10 +3121,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
@@ -3040,10 +3156,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>70</v>
@@ -3075,10 +3191,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>160</v>
@@ -3110,10 +3226,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>450</v>
@@ -3143,9 +3259,114 @@
         <v>45</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <f aca="false">C10/(Weapons!$F$2*(1-F10))</f>
+        <v>55</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <f aca="false">C10/Weapons!$F$3</f>
+        <v>19.25</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <f aca="false">C10/(Weapons!$F$4*(1-F10))</f>
+        <v>36.6666666666667</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>343</v>
+      <c r="A11" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <f aca="false">C11/(Weapons!$F$2*(1-F11))</f>
+        <v>45</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <f aca="false">C11/Weapons!$F$3</f>
+        <v>26.25</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <f aca="false">C11/(Weapons!$F$4*(1-F11))</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <f aca="false">C12/(Weapons!$F$2*(1-F12))</f>
+        <v>120</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <f aca="false">C12/Weapons!$F$3</f>
+        <v>70</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <f aca="false">C12/(Weapons!$F$4*(1-F12))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -3177,30 +3398,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>0.7</v>
@@ -3220,12 +3441,12 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>15</v>
@@ -3245,12 +3466,12 @@
         <v>135</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>0.06</v>
@@ -3270,12 +3491,12 @@
         <v>0.3</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>0.5</v>
@@ -3295,12 +3516,12 @@
         <v>2.5</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>0.1</v>
@@ -3320,12 +3541,12 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>0.08</v>
@@ -3345,12 +3566,12 @@
         <v>0.4</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>1</v>
@@ -3370,21 +3591,21 @@
         <v>5</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3469,7 +3690,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">C14*7</f>
@@ -3482,7 +3703,456 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>368</v>
+        <v>382</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <f aca="false">ROUND(F2*$B$15^1,0)</f>
+        <v>132</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <f aca="false">ROUND(F2*$B$15^2,0)</f>
+        <v>290</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <f aca="false">ROUND(F2*$B$15^3,0)</f>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <f aca="false">ROUND(F3*$B$15^1,0)</f>
+        <v>176</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <f aca="false">ROUND(F3*$B$15^2,0)</f>
+        <v>387</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <f aca="false">ROUND(F3*$B$15^3,0)</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <f aca="false">ROUND(F4*$B$15^1,0)</f>
+        <v>154</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <f aca="false">ROUND(F4*$B$15^2,0)</f>
+        <v>339</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <f aca="false">ROUND(F4*$B$15^3,0)</f>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <f aca="false">ROUND(F5*$B$15^1,0)</f>
+        <v>154</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <f aca="false">ROUND(F5*$B$15^2,0)</f>
+        <v>339</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <f aca="false">ROUND(F5*$B$15^3,0)</f>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <f aca="false">ROUND(F6*$B$15^1,0)</f>
+        <v>198</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <f aca="false">ROUND(F6*$B$15^2,0)</f>
+        <v>436</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <f aca="false">ROUND(F6*$B$15^3,0)</f>
+        <v>958</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <f aca="false">ROUND(F7*$B$15^1,0)</f>
+        <v>176</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <f aca="false">ROUND(F7*$B$15^2,0)</f>
+        <v>387</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <f aca="false">ROUND(F7*$B$15^3,0)</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <f aca="false">ROUND(F8*$B$15^1,0)</f>
+        <v>132</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <f aca="false">ROUND(F8*$B$15^2,0)</f>
+        <v>290</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <f aca="false">ROUND(F8*$B$15^3,0)</f>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <f aca="false">ROUND(F9*$B$15^1,0)</f>
+        <v>220</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <f aca="false">ROUND(F9*$B$15^2,0)</f>
+        <v>484</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <f aca="false">ROUND(F9*$B$15^3,0)</f>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <f aca="false">ROUND(F10*$B$15^1,0)</f>
+        <v>176</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <f aca="false">ROUND(F10*$B$15^2,0)</f>
+        <v>387</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <f aca="false">ROUND(F10*$B$15^3,0)</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <f aca="false">ROUND(F11*$B$15^1,0)</f>
+        <v>154</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <f aca="false">ROUND(F11*$B$15^2,0)</f>
+        <v>339</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <f aca="false">ROUND(F11*$B$15^3,0)</f>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <f aca="false">ROUND(F12*$B$15^1,0)</f>
+        <v>330</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <f aca="false">ROUND(F12*$B$15^2,0)</f>
+        <v>726</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <f aca="false">ROUND(F12*$B$15^3,0)</f>
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -3767,11 +4437,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
@@ -4030,14 +4700,205 @@
         <v>98</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A5-1),0)</f>
+        <v>1250</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C5,0)</f>
+        <v>132</v>
+      </c>
+      <c r="R5" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C5,0)</f>
+        <v>352</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>99</v>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A6-1),0)</f>
+        <v>3125</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C6,0)</f>
+        <v>156</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C6,0)</f>
+        <v>416</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>100</v>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$7*Settings!$B$8^(A7-1),0)</f>
+        <v>7813</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$9*C7,0)</f>
+        <v>180</v>
+      </c>
+      <c r="R7" s="12" t="n">
+        <f aca="false">ROUND(Settings!$B$10*C7,0)</f>
+        <v>480</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4072,54 +4933,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -4131,25 +4992,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>3</v>
@@ -4161,25 +5022,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -4191,28 +5052,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">SUM(D5:D5)</f>
@@ -4221,28 +5082,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">SUM(D5:D6)</f>
@@ -4251,28 +5112,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>900</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -4281,25 +5142,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -4311,25 +5172,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>16</v>
@@ -4341,25 +5202,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>240</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>30</v>
@@ -4371,25 +5232,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
@@ -4401,25 +5262,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.8</v>
@@ -4431,25 +5292,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.55</v>
@@ -4461,7 +5322,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">SUM(D2:D13)</f>
@@ -4496,27 +5357,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -4539,7 +5400,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
@@ -4562,7 +5423,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
@@ -4585,7 +5446,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -4608,7 +5469,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>4</v>
@@ -4631,7 +5492,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -4654,7 +5515,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -4677,7 +5538,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -4700,29 +5561,29 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">C2</f>
@@ -4743,7 +5604,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B14" s="5" t="n">
         <f aca="false">D4</f>
@@ -4764,7 +5625,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">E5</f>
@@ -4785,7 +5646,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4817,15 +5678,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -4833,7 +5694,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>24</v>
@@ -4841,7 +5702,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>68</v>
@@ -4849,7 +5710,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>165</v>
@@ -4857,36 +5718,36 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -4917,7 +5778,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -4948,7 +5809,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
@@ -4979,7 +5840,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>0</v>
@@ -5010,7 +5871,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -5047,60 +5908,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -5146,15 +6007,15 @@
         <v>0.2</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -5200,15 +6061,15 @@
         <v>0.3</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
@@ -5254,15 +6115,15 @@
         <v>0.3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -5308,15 +6169,15 @@
         <v>2</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
@@ -5362,15 +6223,15 @@
         <v>0.6</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
@@ -5416,15 +6277,15 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>2</v>
@@ -5470,15 +6331,15 @@
         <v>0.4</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -5524,15 +6385,15 @@
         <v>5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4</v>
@@ -5578,17 +6439,17 @@
         <v>0.45</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5619,27 +6480,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2</v>
@@ -5662,7 +6523,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>4</v>
@@ -5685,7 +6546,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>5</v>
@@ -5708,7 +6569,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>9</v>
@@ -5731,7 +6592,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
@@ -5754,7 +6615,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1</v>
@@ -5777,7 +6638,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>3</v>
@@ -5800,7 +6661,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>5</v>
@@ -5823,7 +6684,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>8</v>
@@ -5846,7 +6707,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>11</v>
@@ -5869,7 +6730,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -5892,7 +6753,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>10</v>
@@ -5915,7 +6776,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>16</v>
@@ -5961,7 +6822,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5994,37 +6855,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D2" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -6045,14 +6906,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D3" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -6073,14 +6934,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -6101,14 +6962,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -6129,14 +6990,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -6157,14 +7018,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -6185,14 +7046,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -6213,14 +7074,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -6241,14 +7102,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -6269,7 +7130,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balancing.xlsx
+++ b/docs/balancing.xlsx
@@ -24,6 +24,7 @@
     <sheet name="Enemies" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="Flux upgrades" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="Contracts" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Nano-bot crew" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="406">
-  <si>
-    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.11)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="460">
+  <si>
+    <t xml:space="preserve">Bolt &amp; Burrow — balancing sheet (v0.14)</t>
   </si>
   <si>
     <t xml:space="preserve">A planning copy of the numbers in js/config.js. Changing this sheet does NOT change the game:</t>
@@ -91,6 +92,9 @@
     <t xml:space="preserve">Enemies – enemy and boss stats, and how many seconds each weapon takes to beat them</t>
   </si>
   <si>
+    <t xml:space="preserve">Nano-bot crew – loop times and Flux per minute by path length and chips, other jobs per loop, and the daily bot-cache odds</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dig times – seconds to break each block with each arm tier ("—" = too hard for that tier)</t>
   </si>
   <si>
@@ -1253,6 +1257,165 @@
   </si>
   <si>
     <t xml:space="preserve">Three contracts are picked at random each day (same three all day, new ones at midnight). Tier: 0 = start, 1 = Ember Idol home, 2 = Storm Lens home, 3 = Core Heart home (Rustvale).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop base (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seconds every loop takes (CREW.loopBase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per socket (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra seconds for each socket on the path (CREW.loopPerSocket)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest path loop (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A path never loops faster than this before Bus chips: up to 4 sockets loop in 12 s (CREW.pathFloor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No-path loop (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bot with no path bounces around and works this often, with no chip bonuses (CREW.idleLoop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux per loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux job: Flux each loop (CREW.fluxPerLoop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chip bonus Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job work added by a matching chip on the path (CREW.chipBonus[0])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chip bonus Mk II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREW.chipBonus[1] (3 Mk I fuse into 1 Mk II)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chip bonus Overcharged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREW.chipBonus[2], with a drawback (CHIPS.*.over)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus speed Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bot speed added by a Bus chip (CREW.busBonus[0])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old rate (Flux/min per bot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What one nano-bot made in v0.13 (the old NANOBOT.fluxPerMin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sockets on path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flux/min, no chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Flux Amp Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Flux Amps Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus Mk I + rest Flux Amps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs old rate (no chips)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (no path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With no chips a Flux bot makes 10 Flux a minute (the old rate) on any path of up to 4 sockets, or with no path. Sockets past 4 slow the loop, so a long path only pays off with good chips (Mk II, or a Bus).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other jobs (per loop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With one Mk I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With one Mk II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refine (batches)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best recipe the storage can afford; a bonus is a chance of one more batch. Smelt: 35% double output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair (hull)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only when damaged. Patch: ×1.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scout (radius, blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus adds 1.5 blocks per +100%. Scout: +2 and marks gas, vents, unstable rock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haul (radius, blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus adds 1.5 blocks per +100%. Magpie grabs in range all the time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guard (damage, Cave 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage ×(1 + 0.35 × cave number − 1). Sparky chains 60% to a second enemy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily bot-cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREW.daily.uniqueChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pity (guaranteed on cache #)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREW.daily.pity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chance the first unique comes here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average caches per unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days to meet all 8 uniques (no repeats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A lower bound: a unique you already own becomes an Overcharged chip instead</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1557,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1488,6 +1651,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1743,7 +1914,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1861,8 +2032,13 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1892,24 +2068,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">Parts!D6</f>
@@ -1920,12 +2096,12 @@
         <v>-60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">Caves!O2</f>
@@ -1936,12 +2112,12 @@
         <v>-140</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C4" s="12" t="n">
         <f aca="false">Caves!N2</f>
@@ -1952,12 +2128,12 @@
         <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">Parts!D3</f>
@@ -1968,12 +2144,12 @@
         <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">Parts!D9</f>
@@ -1984,12 +2160,12 @@
         <v>-110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">Caves!O3</f>
@@ -2003,7 +2179,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">Caves!N3</f>
@@ -2014,12 +2190,12 @@
         <v>490</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">Parts!D7</f>
@@ -2030,12 +2206,12 @@
         <v>-410</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B10" s="12" t="n">
         <f aca="false">Caves!O4</f>
@@ -2049,7 +2225,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">Caves!N4</f>
@@ -2060,12 +2236,12 @@
         <v>1090</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -2101,27 +2277,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -2137,12 +2313,12 @@
         <v>120</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -2158,12 +2334,12 @@
         <v>75</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -2179,12 +2355,12 @@
         <v>50</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -2200,20 +2376,20 @@
         <v>120</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">$B$12+0</f>
@@ -2222,7 +2398,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B9" s="2" t="n">
         <f aca="false">$B$12+1</f>
@@ -2231,7 +2407,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" s="2" t="n">
         <f aca="false">$B$12+2</f>
@@ -2240,7 +2416,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>3</v>
@@ -2248,50 +2424,50 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
@@ -2330,7 +2506,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>1</v>
@@ -2369,7 +2545,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
@@ -2408,7 +2584,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2</v>
@@ -2447,7 +2623,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -2479,27 +2655,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
@@ -2511,15 +2687,15 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -2531,15 +2707,15 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
@@ -2551,15 +2727,15 @@
         <v>0.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>3</v>
@@ -2571,35 +2747,35 @@
         <v>0.3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -2635,48 +2811,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>0</v>
@@ -2707,18 +2883,18 @@
         <v>3.33333333333333</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>180</v>
@@ -2749,18 +2925,18 @@
         <v>10.2857142857143</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>220</v>
@@ -2791,18 +2967,18 @@
         <v>2.5</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>260</v>
@@ -2833,18 +3009,18 @@
         <v>0.25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>300</v>
@@ -2875,18 +3051,18 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -2900,7 +3076,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
@@ -2914,7 +3090,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2949,42 +3125,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>10</v>
@@ -3016,10 +3192,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>5</v>
@@ -3051,10 +3227,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>14</v>
@@ -3086,10 +3262,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>22</v>
@@ -3121,10 +3297,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
@@ -3156,10 +3332,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>70</v>
@@ -3191,10 +3367,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>160</v>
@@ -3226,10 +3402,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>450</v>
@@ -3261,10 +3437,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>220</v>
@@ -3296,10 +3472,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>300</v>
@@ -3331,10 +3507,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>800</v>
@@ -3366,7 +3542,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3398,30 +3574,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>0.7</v>
@@ -3441,12 +3617,12 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>15</v>
@@ -3466,12 +3642,12 @@
         <v>135</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>0.06</v>
@@ -3491,12 +3667,12 @@
         <v>0.3</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>0.5</v>
@@ -3516,12 +3692,12 @@
         <v>2.5</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>0.1</v>
@@ -3541,12 +3717,12 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>0.08</v>
@@ -3566,12 +3742,12 @@
         <v>0.4</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>1</v>
@@ -3591,21 +3767,21 @@
         <v>5</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3690,7 +3866,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">C14*7</f>
@@ -3703,7 +3879,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -3735,39 +3911,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>40</v>
@@ -3802,7 +3978,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>8</v>
@@ -3837,7 +4013,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -3872,7 +4048,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>4</v>
@@ -3907,7 +4083,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>15</v>
@@ -3942,7 +4118,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>2</v>
@@ -3977,7 +4153,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>150</v>
@@ -4012,7 +4188,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -4047,7 +4223,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>20</v>
@@ -4082,7 +4258,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2</v>
@@ -4117,7 +4293,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4144,7 +4320,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>2.2</v>
@@ -4152,7 +4328,711 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <f aca="false">IF(0=0,$B$5,MAX($B$4,$B$2+$B$3*0))</f>
+        <v>12</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">$B$6*60/B15</f>
+        <v>10</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">IF(0=0,C15,$B$6*(1+$B$7)*60/B15)</f>
+        <v>10</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">IF(0=0,C15,$B$6*(1+0*$B$7)*60/B15)</f>
+        <v>10</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">IF(0&lt;2,E15,$B$6*(1+-1*$B$7)*60/(B15/(1+$B$10)))</f>
+        <v>10</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <f aca="false">C15/$B$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <f aca="false">IF(1=0,$B$5,MAX($B$4,$B$2+$B$3*1))</f>
+        <v>12</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">$B$6*60/B16</f>
+        <v>10</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <f aca="false">IF(1=0,C16,$B$6*(1+$B$7)*60/B16)</f>
+        <v>12.5</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <f aca="false">IF(1=0,C16,$B$6*(1+1*$B$7)*60/B16)</f>
+        <v>12.5</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">IF(1&lt;2,E16,$B$6*(1+0*$B$7)*60/(B16/(1+$B$10)))</f>
+        <v>12.5</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <f aca="false">C16/$B$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="15" t="n">
+        <f aca="false">IF(2=0,$B$5,MAX($B$4,$B$2+$B$3*2))</f>
+        <v>12</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">$B$6*60/B17</f>
+        <v>10</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <f aca="false">IF(2=0,C17,$B$6*(1+$B$7)*60/B17)</f>
+        <v>12.5</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <f aca="false">IF(2=0,C17,$B$6*(1+2*$B$7)*60/B17)</f>
+        <v>15</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">IF(2&lt;2,E17,$B$6*(1+1*$B$7)*60/(B17/(1+$B$10)))</f>
+        <v>14.375</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <f aca="false">C17/$B$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="15" t="n">
+        <f aca="false">IF(3=0,$B$5,MAX($B$4,$B$2+$B$3*3))</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <f aca="false">$B$6*60/B18</f>
+        <v>10</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <f aca="false">IF(3=0,C18,$B$6*(1+$B$7)*60/B18)</f>
+        <v>12.5</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <f aca="false">IF(3=0,C18,$B$6*(1+3*$B$7)*60/B18)</f>
+        <v>17.5</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <f aca="false">IF(3&lt;2,E18,$B$6*(1+2*$B$7)*60/(B18/(1+$B$10)))</f>
+        <v>17.25</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <f aca="false">C18/$B$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="15" t="n">
+        <f aca="false">IF(4=0,$B$5,MAX($B$4,$B$2+$B$3*4))</f>
+        <v>12</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">$B$6*60/B19</f>
+        <v>10</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <f aca="false">IF(4=0,C19,$B$6*(1+$B$7)*60/B19)</f>
+        <v>12.5</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <f aca="false">IF(4=0,C19,$B$6*(1+4*$B$7)*60/B19)</f>
+        <v>20</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <f aca="false">IF(4&lt;2,E19,$B$6*(1+3*$B$7)*60/(B19/(1+$B$10)))</f>
+        <v>20.125</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <f aca="false">C19/$B$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <f aca="false">IF(5=0,$B$5,MAX($B$4,$B$2+$B$3*5))</f>
+        <v>13.5</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <f aca="false">$B$6*60/B20</f>
+        <v>8.88888888888889</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <f aca="false">IF(5=0,C20,$B$6*(1+$B$7)*60/B20)</f>
+        <v>11.1111111111111</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <f aca="false">IF(5=0,C20,$B$6*(1+5*$B$7)*60/B20)</f>
+        <v>20</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <f aca="false">IF(5&lt;2,E20,$B$6*(1+4*$B$7)*60/(B20/(1+$B$10)))</f>
+        <v>20.4444444444444</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <f aca="false">C20/$B$11</f>
+        <v>0.888888888888889</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="15" t="n">
+        <f aca="false">IF(6=0,$B$5,MAX($B$4,$B$2+$B$3*6))</f>
+        <v>15</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <f aca="false">$B$6*60/B21</f>
+        <v>8</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <f aca="false">IF(6=0,C21,$B$6*(1+$B$7)*60/B21)</f>
+        <v>10</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <f aca="false">IF(6=0,C21,$B$6*(1+6*$B$7)*60/B21)</f>
+        <v>20</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <f aca="false">IF(6&lt;2,E21,$B$6*(1+5*$B$7)*60/(B21/(1+$B$10)))</f>
+        <v>20.7</v>
+      </c>
+      <c r="G21" s="22" t="n">
+        <f aca="false">C21/$B$11</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="15" t="n">
+        <f aca="false">IF(7=0,$B$5,MAX($B$4,$B$2+$B$3*7))</f>
+        <v>16.5</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <f aca="false">$B$6*60/B22</f>
+        <v>7.27272727272727</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <f aca="false">IF(7=0,C22,$B$6*(1+$B$7)*60/B22)</f>
+        <v>9.09090909090909</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <f aca="false">IF(7=0,C22,$B$6*(1+7*$B$7)*60/B22)</f>
+        <v>20</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <f aca="false">IF(7&lt;2,E22,$B$6*(1+6*$B$7)*60/(B22/(1+$B$10)))</f>
+        <v>20.9090909090909</v>
+      </c>
+      <c r="G22" s="22" t="n">
+        <f aca="false">C22/$B$11</f>
+        <v>0.727272727272727</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="15" t="n">
+        <f aca="false">IF(8=0,$B$5,MAX($B$4,$B$2+$B$3*8))</f>
+        <v>18</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">$B$6*60/B23</f>
+        <v>6.66666666666667</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <f aca="false">IF(8=0,C23,$B$6*(1+$B$7)*60/B23)</f>
+        <v>8.33333333333333</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <f aca="false">IF(8=0,C23,$B$6*(1+8*$B$7)*60/B23)</f>
+        <v>20</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <f aca="false">IF(8&lt;2,E23,$B$6*(1+7*$B$7)*60/(B23/(1+$B$10)))</f>
+        <v>21.0833333333333</v>
+      </c>
+      <c r="G23" s="22" t="n">
+        <f aca="false">C23/$B$11</f>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="24" t="n">
+        <f aca="false">B28*(1+$B$7)</f>
+        <v>1.25</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">B28*(1+$B$8)</f>
+        <v>1.6</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="24" t="n">
+        <f aca="false">B29*(1+$B$7)</f>
+        <v>3.75</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <f aca="false">B29*(1+$B$8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <f aca="false">B30+1.5*$B$7</f>
+        <v>4.375</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <f aca="false">B30+1.5*$B$8</f>
+        <v>4.9</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="15" t="n">
+        <f aca="false">B31+1.5*$B$7</f>
+        <v>4.375</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <f aca="false">B31+1.5*$B$8</f>
+        <v>4.9</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <f aca="false">B32*(1+$B$7)</f>
+        <v>3.125</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <f aca="false">B32*(1+$B$8)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="25" t="n">
+        <f aca="false">IF(A40&lt;$B$37,(1-$B$36)^(A40-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.2</v>
+      </c>
+      <c r="C40" s="25" t="n">
+        <f aca="false">SUM($B$40:B40)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="25" t="n">
+        <f aca="false">IF(A41&lt;$B$37,(1-$B$36)^(A41-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.16</v>
+      </c>
+      <c r="C41" s="25" t="n">
+        <f aca="false">SUM($B$40:B41)</f>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="25" t="n">
+        <f aca="false">IF(A42&lt;$B$37,(1-$B$36)^(A42-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.128</v>
+      </c>
+      <c r="C42" s="25" t="n">
+        <f aca="false">SUM($B$40:B42)</f>
+        <v>0.488</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" s="25" t="n">
+        <f aca="false">IF(A43&lt;$B$37,(1-$B$36)^(A43-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.1024</v>
+      </c>
+      <c r="C43" s="25" t="n">
+        <f aca="false">SUM($B$40:B43)</f>
+        <v>0.5904</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" s="25" t="n">
+        <f aca="false">IF(A44&lt;$B$37,(1-$B$36)^(A44-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.08192</v>
+      </c>
+      <c r="C44" s="25" t="n">
+        <f aca="false">SUM($B$40:B44)</f>
+        <v>0.67232</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" s="25" t="n">
+        <f aca="false">IF(A45&lt;$B$37,(1-$B$36)^(A45-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.065536</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <f aca="false">SUM($B$40:B45)</f>
+        <v>0.737856</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="25" t="n">
+        <f aca="false">IF(A46&lt;$B$37,(1-$B$36)^(A46-1)*$B$36,(1-$B$36)^($B$37-1))</f>
+        <v>0.262144</v>
+      </c>
+      <c r="C46" s="25" t="n">
+        <f aca="false">SUM($B$40:B46)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B48" s="24" t="n">
+        <f aca="false">SUMPRODUCT(A40:A46,B40:B46)</f>
+        <v>3.951424</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B49" s="17" t="n">
+        <f aca="false">B48*8</f>
+        <v>31.611392</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -4181,244 +5061,244 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>80</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>60</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>160</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>75</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4457,61 +5337,61 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4519,19 +5399,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>0.025</v>
@@ -4552,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N2" s="11" t="n">
         <v>300</v>
@@ -4573,7 +5453,7 @@
         <v>160</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4581,19 +5461,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>0.03</v>
@@ -4614,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" s="11" t="n">
         <v>800</v>
@@ -4635,7 +5515,7 @@
         <v>240</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4643,19 +5523,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>0.025</v>
@@ -4676,7 +5556,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="11" t="n">
         <v>2000</v>
@@ -4697,7 +5577,7 @@
         <v>320</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,19 +5585,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.045</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.02</v>
@@ -4738,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" s="11" t="n">
         <v>2500</v>
@@ -4759,7 +5639,7 @@
         <v>352</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,19 +5647,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>2.6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0.045</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>0.015</v>
@@ -4800,7 +5680,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N6" s="11" t="n">
         <v>4000</v>
@@ -4821,7 +5701,7 @@
         <v>416</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4829,19 +5709,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0.05</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.035</v>
@@ -4862,7 +5742,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="11" t="n">
         <v>6000</v>
@@ -4883,22 +5763,22 @@
         <v>480</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4933,54 +5813,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>0</v>
@@ -4992,25 +5872,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>3</v>
@@ -5022,25 +5902,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -5052,28 +5932,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">SUM(D5:D5)</f>
@@ -5082,28 +5962,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">SUM(D5:D6)</f>
@@ -5112,28 +5992,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>900</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -5142,25 +6022,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -5172,25 +6052,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>150</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>16</v>
@@ -5202,25 +6082,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>240</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>30</v>
@@ -5232,25 +6112,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>1</v>
@@ -5262,25 +6142,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>0.8</v>
@@ -5292,25 +6172,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0.55</v>
@@ -5322,7 +6202,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">SUM(D2:D13)</f>
@@ -5357,27 +6237,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -5400,7 +6280,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
@@ -5423,7 +6303,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
@@ -5446,7 +6326,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -5469,7 +6349,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>4</v>
@@ -5492,7 +6372,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -5515,7 +6395,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -5538,7 +6418,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -5561,29 +6441,29 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">C2</f>
@@ -5604,7 +6484,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" s="5" t="n">
         <f aca="false">D4</f>
@@ -5625,7 +6505,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">E5</f>
@@ -5646,7 +6526,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5678,15 +6558,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -5694,7 +6574,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>24</v>
@@ -5702,7 +6582,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>68</v>
@@ -5710,7 +6590,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>165</v>
@@ -5718,36 +6598,36 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="F7" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>2</v>
@@ -5778,7 +6658,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1</v>
@@ -5809,7 +6689,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
@@ -5840,7 +6720,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>0</v>
@@ -5871,7 +6751,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5908,60 +6788,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -6007,15 +6887,15 @@
         <v>0.2</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -6061,15 +6941,15 @@
         <v>0.3</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
@@ -6115,15 +6995,15 @@
         <v>0.3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -6169,15 +7049,15 @@
         <v>2</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
@@ -6223,15 +7103,15 @@
         <v>0.6</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
@@ -6277,15 +7157,15 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>2</v>
@@ -6331,15 +7211,15 @@
         <v>0.4</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -6385,15 +7265,15 @@
         <v>5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4</v>
@@ -6439,17 +7319,17 @@
         <v>0.45</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -6480,27 +7360,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2</v>
@@ -6523,7 +7403,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>4</v>
@@ -6546,7 +7426,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>5</v>
@@ -6569,7 +7449,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>9</v>
@@ -6592,7 +7472,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
@@ -6615,7 +7495,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1</v>
@@ -6638,7 +7518,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>3</v>
@@ -6661,7 +7541,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>5</v>
@@ -6684,7 +7564,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>8</v>
@@ -6707,7 +7587,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>11</v>
@@ -6730,7 +7610,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -6753,7 +7633,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>10</v>
@@ -6776,7 +7656,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>16</v>
@@ -6799,7 +7679,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>40</v>
@@ -6822,7 +7702,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -6855,37 +7735,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -6906,14 +7786,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -6934,14 +7814,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">Parts!$F$8</f>
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -6962,14 +7842,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -6990,14 +7870,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -7018,14 +7898,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">Parts!$F$9</f>
         <v>140</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -7046,14 +7926,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">Parts!$H$11</f>
@@ -7074,14 +7954,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">Parts!$H$12</f>
@@ -7102,14 +7982,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">Parts!$F$10</f>
         <v>240</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">Parts!$H$13</f>
@@ -7130,7 +8010,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
